--- a/artfynd/A 30443-2025 artfynd.xlsx
+++ b/artfynd/A 30443-2025 artfynd.xlsx
@@ -1864,7 +1864,7 @@
         <v>126908435</v>
       </c>
       <c r="B11" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1958,45 +1958,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126909177</v>
+        <v>126907068</v>
       </c>
       <c r="B12" t="n">
-        <v>91245</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691383</v>
+        <v>691392</v>
       </c>
       <c r="R12" t="n">
-        <v>6657798</v>
+        <v>6657918</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2055,54 +2064,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126907068</v>
+        <v>126909177</v>
       </c>
       <c r="B13" t="n">
-        <v>98361</v>
+        <v>91319</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691392</v>
+        <v>691383</v>
       </c>
       <c r="R13" t="n">
-        <v>6657918</v>
+        <v>6657798</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2161,54 +2161,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126907789</v>
+        <v>126906462</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>5176</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691381</v>
+        <v>691433</v>
       </c>
       <c r="R14" t="n">
-        <v>6658051</v>
+        <v>6657859</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2267,45 +2258,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126906462</v>
+        <v>126907789</v>
       </c>
       <c r="B15" t="n">
-        <v>5176</v>
+        <v>98436</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691433</v>
+        <v>691381</v>
       </c>
       <c r="R15" t="n">
-        <v>6657859</v>
+        <v>6658051</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2367,7 +2367,7 @@
         <v>126908037</v>
       </c>
       <c r="B16" t="n">
-        <v>95810</v>
+        <v>95885</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2470,57 +2470,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126907030</v>
+        <v>126908154</v>
       </c>
       <c r="B17" t="n">
-        <v>98361</v>
+        <v>91319</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691371</v>
+        <v>691373</v>
       </c>
       <c r="R17" t="n">
-        <v>6657926</v>
+        <v>6658096</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2576,10 +2567,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126908926</v>
+        <v>126907984</v>
       </c>
       <c r="B18" t="n">
-        <v>8436</v>
+        <v>95789</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,21 +2578,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>2818</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2611,13 +2602,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691339</v>
+        <v>691394</v>
       </c>
       <c r="R18" t="n">
-        <v>6657957</v>
+        <v>6658034</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2673,45 +2664,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126907984</v>
+        <v>126906047</v>
       </c>
       <c r="B19" t="n">
-        <v>95714</v>
+        <v>91319</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691394</v>
+        <v>691432</v>
       </c>
       <c r="R19" t="n">
-        <v>6658034</v>
+        <v>6657786</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2770,48 +2761,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126908154</v>
+        <v>126907030</v>
       </c>
       <c r="B20" t="n">
-        <v>91245</v>
+        <v>98436</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691373</v>
+        <v>691371</v>
       </c>
       <c r="R20" t="n">
-        <v>6658096</v>
+        <v>6657926</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2867,48 +2867,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126906047</v>
+        <v>126908926</v>
       </c>
       <c r="B21" t="n">
-        <v>91245</v>
+        <v>8436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691432</v>
+        <v>691339</v>
       </c>
       <c r="R21" t="n">
-        <v>6657786</v>
+        <v>6657957</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>126909047</v>
       </c>
       <c r="B23" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>126907497</v>
       </c>
       <c r="B24" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>126905851</v>
       </c>
       <c r="B25" t="n">
-        <v>91874</v>
+        <v>91948</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,45 +3376,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126905916</v>
+        <v>126908119</v>
       </c>
       <c r="B26" t="n">
-        <v>84969</v>
+        <v>98436</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1971</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stor sotdyna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Camarops polysperma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Mont.) J.H.Mill.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691453</v>
+        <v>691366</v>
       </c>
       <c r="R26" t="n">
-        <v>6657774</v>
+        <v>6658076</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3473,54 +3482,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126908119</v>
+        <v>126905916</v>
       </c>
       <c r="B27" t="n">
-        <v>98361</v>
+        <v>85033</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1971</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor sotdyna</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Camarops polysperma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Mont.) J.H.Mill.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691366</v>
+        <v>691453</v>
       </c>
       <c r="R27" t="n">
-        <v>6658076</v>
+        <v>6657774</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3582,7 +3582,7 @@
         <v>126909251</v>
       </c>
       <c r="B28" t="n">
-        <v>84969</v>
+        <v>85033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>126909137</v>
       </c>
       <c r="B29" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>126909234</v>
       </c>
       <c r="B30" t="n">
-        <v>80043</v>
+        <v>80074</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>126908832</v>
       </c>
       <c r="B31" t="n">
-        <v>100543</v>
+        <v>100618</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>126907198</v>
       </c>
       <c r="B33" t="n">
-        <v>97239</v>
+        <v>97314</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>126908052</v>
       </c>
       <c r="B34" t="n">
-        <v>100543</v>
+        <v>100618</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>126906062</v>
       </c>
       <c r="B35" t="n">
-        <v>91259</v>
+        <v>91333</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>126908608</v>
       </c>
       <c r="B36" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>126906629</v>
       </c>
       <c r="B37" t="n">
-        <v>105396</v>
+        <v>105471</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>126907715</v>
       </c>
       <c r="B38" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126908912</v>
+        <v>126907654</v>
       </c>
       <c r="B39" t="n">
         <v>5176</v>
@@ -4722,17 +4722,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691331</v>
+        <v>691381</v>
       </c>
       <c r="R39" t="n">
-        <v>6657987</v>
+        <v>6658039</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126907654</v>
+        <v>126908912</v>
       </c>
       <c r="B40" t="n">
         <v>5176</v>
@@ -4819,17 +4819,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>691381</v>
+        <v>691331</v>
       </c>
       <c r="R40" t="n">
-        <v>6658039</v>
+        <v>6657987</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>126907755</v>
       </c>
       <c r="B42" t="n">
-        <v>105396</v>
+        <v>105471</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5093,10 +5093,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126909078</v>
+        <v>126907354</v>
       </c>
       <c r="B43" t="n">
-        <v>8436</v>
+        <v>91948</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5104,37 +5104,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106554</v>
+        <v>1339</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>691347</v>
+        <v>691389</v>
       </c>
       <c r="R43" t="n">
-        <v>6657905</v>
+        <v>6657968</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5174,6 +5174,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5292,10 +5307,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126907354</v>
+        <v>126909078</v>
       </c>
       <c r="B45" t="n">
-        <v>91874</v>
+        <v>8436</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5303,37 +5318,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1339</v>
+        <v>106554</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691389</v>
+        <v>691347</v>
       </c>
       <c r="R45" t="n">
-        <v>6657968</v>
+        <v>6657905</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5373,21 +5388,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5504,7 +5504,7 @@
         <v>126908462</v>
       </c>
       <c r="B47" t="n">
-        <v>105396</v>
+        <v>105471</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>126906874</v>
       </c>
       <c r="B48" t="n">
-        <v>95714</v>
+        <v>95789</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>126908159</v>
       </c>
       <c r="B49" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5806,54 +5806,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126906755</v>
+        <v>126909066</v>
       </c>
       <c r="B50" t="n">
-        <v>98361</v>
+        <v>5176</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691376</v>
+        <v>691337</v>
       </c>
       <c r="R50" t="n">
-        <v>6657865</v>
+        <v>6657892</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5912,45 +5903,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126909066</v>
+        <v>126906755</v>
       </c>
       <c r="B51" t="n">
-        <v>5176</v>
+        <v>98436</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>691337</v>
+        <v>691376</v>
       </c>
       <c r="R51" t="n">
-        <v>6657892</v>
+        <v>6657865</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6009,45 +6009,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126908952</v>
+        <v>126908908</v>
       </c>
       <c r="B52" t="n">
-        <v>8436</v>
+        <v>98436</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>691329</v>
+        <v>691331</v>
       </c>
       <c r="R52" t="n">
-        <v>6657950</v>
+        <v>6657987</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6106,54 +6115,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126908908</v>
+        <v>126907554</v>
       </c>
       <c r="B53" t="n">
-        <v>98361</v>
+        <v>5196</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>691331</v>
+        <v>691373</v>
       </c>
       <c r="R53" t="n">
-        <v>6657987</v>
+        <v>6658009</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6212,10 +6212,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126907554</v>
+        <v>126908952</v>
       </c>
       <c r="B54" t="n">
-        <v>5196</v>
+        <v>8436</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6223,34 +6223,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>691373</v>
+        <v>691329</v>
       </c>
       <c r="R54" t="n">
-        <v>6658009</v>
+        <v>6657950</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6312,7 +6312,7 @@
         <v>126909033</v>
       </c>
       <c r="B55" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>126907301</v>
       </c>
       <c r="B56" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>126908731</v>
       </c>
       <c r="B57" t="n">
-        <v>90782</v>
+        <v>90856</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6618,32 +6618,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126907130</v>
+        <v>126907540</v>
       </c>
       <c r="B58" t="n">
-        <v>8436</v>
+        <v>91677</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106554</v>
+        <v>2062</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>691416</v>
+        <v>691377</v>
       </c>
       <c r="R58" t="n">
-        <v>6657910</v>
+        <v>6658022</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>126908472</v>
       </c>
       <c r="B59" t="n">
-        <v>91874</v>
+        <v>91948</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6812,32 +6812,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126907540</v>
+        <v>126907130</v>
       </c>
       <c r="B60" t="n">
-        <v>91603</v>
+        <v>8436</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2062</v>
+        <v>106554</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6847,10 +6847,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>691377</v>
+        <v>691416</v>
       </c>
       <c r="R60" t="n">
-        <v>6658022</v>
+        <v>6657910</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6909,10 +6909,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126908164</v>
+        <v>126906449</v>
       </c>
       <c r="B61" t="n">
-        <v>5176</v>
+        <v>91284</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6920,37 +6920,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>691373</v>
+        <v>691433</v>
       </c>
       <c r="R61" t="n">
-        <v>6658096</v>
+        <v>6657859</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7006,10 +7006,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126906449</v>
+        <v>126908164</v>
       </c>
       <c r="B62" t="n">
-        <v>91210</v>
+        <v>5176</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7017,37 +7017,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>691433</v>
+        <v>691373</v>
       </c>
       <c r="R62" t="n">
-        <v>6657859</v>
+        <v>6658096</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>126951967</v>
       </c>
       <c r="B63" t="n">
-        <v>105215</v>
+        <v>105290</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 30443-2025 artfynd.xlsx
+++ b/artfynd/A 30443-2025 artfynd.xlsx
@@ -1864,7 +1864,7 @@
         <v>126908435</v>
       </c>
       <c r="B11" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1958,54 +1958,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126907068</v>
+        <v>126909177</v>
       </c>
       <c r="B12" t="n">
-        <v>98436</v>
+        <v>91325</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691392</v>
+        <v>691383</v>
       </c>
       <c r="R12" t="n">
-        <v>6657918</v>
+        <v>6657798</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2064,45 +2055,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126909177</v>
+        <v>126907068</v>
       </c>
       <c r="B13" t="n">
-        <v>91319</v>
+        <v>98442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691383</v>
+        <v>691392</v>
       </c>
       <c r="R13" t="n">
-        <v>6657798</v>
+        <v>6657918</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2161,45 +2161,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126906462</v>
+        <v>126907789</v>
       </c>
       <c r="B14" t="n">
-        <v>5176</v>
+        <v>98442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691433</v>
+        <v>691381</v>
       </c>
       <c r="R14" t="n">
-        <v>6657859</v>
+        <v>6658051</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2258,54 +2267,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126907789</v>
+        <v>126906462</v>
       </c>
       <c r="B15" t="n">
-        <v>98436</v>
+        <v>5176</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691381</v>
+        <v>691433</v>
       </c>
       <c r="R15" t="n">
-        <v>6658051</v>
+        <v>6657859</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2364,10 +2364,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126908037</v>
+        <v>126907984</v>
       </c>
       <c r="B16" t="n">
-        <v>95885</v>
+        <v>95795</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,46 +2375,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691381</v>
+        <v>691394</v>
       </c>
       <c r="R16" t="n">
-        <v>6658051</v>
+        <v>6658034</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2470,32 +2461,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126908154</v>
+        <v>126908926</v>
       </c>
       <c r="B17" t="n">
-        <v>91319</v>
+        <v>8436</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2505,13 +2496,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691373</v>
+        <v>691339</v>
       </c>
       <c r="R17" t="n">
-        <v>6658096</v>
+        <v>6657957</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2567,10 +2558,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126907984</v>
+        <v>126908037</v>
       </c>
       <c r="B18" t="n">
-        <v>95789</v>
+        <v>95891</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,37 +2569,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691394</v>
+        <v>691381</v>
       </c>
       <c r="R18" t="n">
-        <v>6658034</v>
+        <v>6658051</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>126906047</v>
       </c>
       <c r="B19" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>126907030</v>
       </c>
       <c r="B20" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2867,32 +2867,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126908926</v>
+        <v>126908154</v>
       </c>
       <c r="B21" t="n">
-        <v>8436</v>
+        <v>91325</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2902,13 +2902,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691339</v>
+        <v>691373</v>
       </c>
       <c r="R21" t="n">
-        <v>6657957</v>
+        <v>6658096</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>126909047</v>
       </c>
       <c r="B23" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>126907497</v>
       </c>
       <c r="B24" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>126905851</v>
       </c>
       <c r="B25" t="n">
-        <v>91948</v>
+        <v>91954</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,54 +3376,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126908119</v>
+        <v>126909251</v>
       </c>
       <c r="B26" t="n">
-        <v>98436</v>
+        <v>85036</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1971</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor sotdyna</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Camarops polysperma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Mont.) J.H.Mill.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691366</v>
+        <v>691377</v>
       </c>
       <c r="R26" t="n">
-        <v>6658076</v>
+        <v>6657778</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3485,7 +3476,7 @@
         <v>126905916</v>
       </c>
       <c r="B27" t="n">
-        <v>85033</v>
+        <v>85036</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3579,45 +3570,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126909251</v>
+        <v>126908119</v>
       </c>
       <c r="B28" t="n">
-        <v>85033</v>
+        <v>98442</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1971</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stor sotdyna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Camarops polysperma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Mont.) J.H.Mill.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>691377</v>
+        <v>691366</v>
       </c>
       <c r="R28" t="n">
-        <v>6657778</v>
+        <v>6658076</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3676,54 +3676,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126909137</v>
+        <v>126908832</v>
       </c>
       <c r="B29" t="n">
-        <v>98436</v>
+        <v>100624</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691384</v>
+        <v>691331</v>
       </c>
       <c r="R29" t="n">
-        <v>6657854</v>
+        <v>6657987</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3785,7 +3776,7 @@
         <v>126909234</v>
       </c>
       <c r="B30" t="n">
-        <v>80074</v>
+        <v>80077</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3879,45 +3870,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126908832</v>
+        <v>126909137</v>
       </c>
       <c r="B31" t="n">
-        <v>100618</v>
+        <v>98442</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691331</v>
+        <v>691384</v>
       </c>
       <c r="R31" t="n">
-        <v>6657987</v>
+        <v>6657854</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4076,7 +4076,7 @@
         <v>126907198</v>
       </c>
       <c r="B33" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>126908052</v>
       </c>
       <c r="B34" t="n">
-        <v>100618</v>
+        <v>100624</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4276,45 +4276,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126906062</v>
+        <v>126908608</v>
       </c>
       <c r="B35" t="n">
-        <v>91333</v>
+        <v>98442</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>691432</v>
+        <v>691329</v>
       </c>
       <c r="R35" t="n">
-        <v>6657786</v>
+        <v>6658013</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4373,37 +4382,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126908608</v>
+        <v>126906629</v>
       </c>
       <c r="B36" t="n">
-        <v>98436</v>
+        <v>105477</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4413,17 +4422,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691329</v>
+        <v>691376</v>
       </c>
       <c r="R36" t="n">
-        <v>6658013</v>
+        <v>6657865</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4479,57 +4488,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126906629</v>
+        <v>126906062</v>
       </c>
       <c r="B37" t="n">
-        <v>105471</v>
+        <v>91339</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221144</v>
+        <v>1204</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691376</v>
+        <v>691432</v>
       </c>
       <c r="R37" t="n">
-        <v>6657865</v>
+        <v>6657786</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4585,54 +4585,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126907715</v>
+        <v>126907654</v>
       </c>
       <c r="B38" t="n">
-        <v>98436</v>
+        <v>5176</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691363</v>
+        <v>691381</v>
       </c>
       <c r="R38" t="n">
-        <v>6658060</v>
+        <v>6658039</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4691,7 +4682,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126907654</v>
+        <v>126908912</v>
       </c>
       <c r="B39" t="n">
         <v>5176</v>
@@ -4722,17 +4713,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691381</v>
+        <v>691331</v>
       </c>
       <c r="R39" t="n">
-        <v>6658039</v>
+        <v>6657987</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4788,48 +4779,57 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126908912</v>
+        <v>126907715</v>
       </c>
       <c r="B40" t="n">
-        <v>5176</v>
+        <v>98442</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>691331</v>
+        <v>691363</v>
       </c>
       <c r="R40" t="n">
-        <v>6657987</v>
+        <v>6658060</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>126907755</v>
       </c>
       <c r="B42" t="n">
-        <v>105471</v>
+        <v>105477</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5093,48 +5093,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126907354</v>
+        <v>126908871</v>
       </c>
       <c r="B43" t="n">
-        <v>91948</v>
+        <v>57654</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>691389</v>
+        <v>691352</v>
       </c>
       <c r="R43" t="n">
-        <v>6657968</v>
+        <v>6657981</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5174,21 +5179,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5205,53 +5195,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126908871</v>
+        <v>126907354</v>
       </c>
       <c r="B44" t="n">
-        <v>57654</v>
+        <v>91954</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691352</v>
+        <v>691389</v>
       </c>
       <c r="R44" t="n">
-        <v>6657981</v>
+        <v>6657968</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5291,6 +5276,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5307,10 +5307,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126909078</v>
+        <v>126908462</v>
       </c>
       <c r="B45" t="n">
-        <v>8436</v>
+        <v>105477</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5318,37 +5318,46 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106554</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691347</v>
+        <v>691296</v>
       </c>
       <c r="R45" t="n">
-        <v>6657905</v>
+        <v>6658183</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5378,6 +5387,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Cirka</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5404,7 +5418,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126907007</v>
+        <v>126909078</v>
       </c>
       <c r="B46" t="n">
         <v>8436</v>
@@ -5435,14 +5449,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691368</v>
+        <v>691347</v>
       </c>
       <c r="R46" t="n">
-        <v>6657895</v>
+        <v>6657905</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5501,10 +5515,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126908462</v>
+        <v>126907007</v>
       </c>
       <c r="B47" t="n">
-        <v>105471</v>
+        <v>8436</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5512,46 +5526,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>106554</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>691296</v>
+        <v>691368</v>
       </c>
       <c r="R47" t="n">
-        <v>6658183</v>
+        <v>6657895</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5581,11 +5586,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Cirka</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5612,10 +5612,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126906874</v>
+        <v>126909066</v>
       </c>
       <c r="B48" t="n">
-        <v>95789</v>
+        <v>5176</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5623,37 +5623,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>691382</v>
+        <v>691337</v>
       </c>
       <c r="R48" t="n">
-        <v>6657874</v>
+        <v>6657892</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>126908159</v>
       </c>
       <c r="B49" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5806,10 +5806,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126909066</v>
+        <v>126906874</v>
       </c>
       <c r="B50" t="n">
-        <v>5176</v>
+        <v>95795</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5817,37 +5817,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691337</v>
+        <v>691382</v>
       </c>
       <c r="R50" t="n">
-        <v>6657892</v>
+        <v>6657874</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>126906755</v>
       </c>
       <c r="B51" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6009,54 +6009,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126908908</v>
+        <v>126908952</v>
       </c>
       <c r="B52" t="n">
-        <v>98436</v>
+        <v>8436</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>691331</v>
+        <v>691329</v>
       </c>
       <c r="R52" t="n">
-        <v>6657987</v>
+        <v>6657950</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6212,45 +6203,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126908952</v>
+        <v>126908908</v>
       </c>
       <c r="B54" t="n">
-        <v>8436</v>
+        <v>98442</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>691329</v>
+        <v>691331</v>
       </c>
       <c r="R54" t="n">
-        <v>6657950</v>
+        <v>6657987</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6312,7 +6312,7 @@
         <v>126909033</v>
       </c>
       <c r="B55" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>126907301</v>
       </c>
       <c r="B56" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>126908731</v>
       </c>
       <c r="B57" t="n">
-        <v>90856</v>
+        <v>90862</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>126907540</v>
       </c>
       <c r="B58" t="n">
-        <v>91677</v>
+        <v>91683</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>126908472</v>
       </c>
       <c r="B59" t="n">
-        <v>91948</v>
+        <v>91954</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6909,10 +6909,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126906449</v>
+        <v>126908164</v>
       </c>
       <c r="B61" t="n">
-        <v>91284</v>
+        <v>5176</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6920,37 +6920,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>691433</v>
+        <v>691373</v>
       </c>
       <c r="R61" t="n">
-        <v>6657859</v>
+        <v>6658096</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7006,10 +7006,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126908164</v>
+        <v>126906449</v>
       </c>
       <c r="B62" t="n">
-        <v>5176</v>
+        <v>91290</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7017,37 +7017,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>691373</v>
+        <v>691433</v>
       </c>
       <c r="R62" t="n">
-        <v>6658096</v>
+        <v>6657859</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>126951967</v>
       </c>
       <c r="B63" t="n">
-        <v>105290</v>
+        <v>105296</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 30443-2025 artfynd.xlsx
+++ b/artfynd/A 30443-2025 artfynd.xlsx
@@ -2161,54 +2161,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126907789</v>
+        <v>126906462</v>
       </c>
       <c r="B14" t="n">
-        <v>98442</v>
+        <v>5176</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691381</v>
+        <v>691433</v>
       </c>
       <c r="R14" t="n">
-        <v>6658051</v>
+        <v>6657859</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2267,45 +2258,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126906462</v>
+        <v>126907789</v>
       </c>
       <c r="B15" t="n">
-        <v>5176</v>
+        <v>98442</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691433</v>
+        <v>691381</v>
       </c>
       <c r="R15" t="n">
-        <v>6657859</v>
+        <v>6658051</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2461,10 +2461,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126908926</v>
+        <v>126908037</v>
       </c>
       <c r="B17" t="n">
-        <v>8436</v>
+        <v>95891</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2472,34 +2472,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106554</v>
+        <v>210</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691339</v>
+        <v>691381</v>
       </c>
       <c r="R17" t="n">
-        <v>6657957</v>
+        <v>6658051</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2558,57 +2567,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126908037</v>
+        <v>126908154</v>
       </c>
       <c r="B18" t="n">
-        <v>95891</v>
+        <v>91325</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>210</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691381</v>
+        <v>691373</v>
       </c>
       <c r="R18" t="n">
-        <v>6658051</v>
+        <v>6658096</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2761,54 +2761,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126907030</v>
+        <v>126908926</v>
       </c>
       <c r="B20" t="n">
-        <v>98442</v>
+        <v>8436</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691371</v>
+        <v>691339</v>
       </c>
       <c r="R20" t="n">
-        <v>6657926</v>
+        <v>6657957</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2867,48 +2858,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126908154</v>
+        <v>126907030</v>
       </c>
       <c r="B21" t="n">
-        <v>91325</v>
+        <v>98442</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691373</v>
+        <v>691371</v>
       </c>
       <c r="R21" t="n">
-        <v>6658096</v>
+        <v>6657926</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3167,32 +3167,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126907497</v>
+        <v>126905851</v>
       </c>
       <c r="B24" t="n">
-        <v>91325</v>
+        <v>91954</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691377</v>
+        <v>691458</v>
       </c>
       <c r="R24" t="n">
-        <v>6658022</v>
+        <v>6657753</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3248,6 +3248,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3264,32 +3279,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126905851</v>
+        <v>126907497</v>
       </c>
       <c r="B25" t="n">
-        <v>91954</v>
+        <v>91325</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3299,10 +3314,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691458</v>
+        <v>691377</v>
       </c>
       <c r="R25" t="n">
-        <v>6657753</v>
+        <v>6658022</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3345,21 +3360,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3376,45 +3376,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126909251</v>
+        <v>126908119</v>
       </c>
       <c r="B26" t="n">
-        <v>85036</v>
+        <v>98442</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1971</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stor sotdyna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Camarops polysperma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Mont.) J.H.Mill.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691377</v>
+        <v>691366</v>
       </c>
       <c r="R26" t="n">
-        <v>6657778</v>
+        <v>6658076</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3473,7 +3482,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126905916</v>
+        <v>126909251</v>
       </c>
       <c r="B27" t="n">
         <v>85036</v>
@@ -3508,10 +3517,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691453</v>
+        <v>691377</v>
       </c>
       <c r="R27" t="n">
-        <v>6657774</v>
+        <v>6657778</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3570,54 +3579,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126908119</v>
+        <v>126905916</v>
       </c>
       <c r="B28" t="n">
-        <v>98442</v>
+        <v>85036</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1971</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor sotdyna</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Camarops polysperma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Mont.) J.H.Mill.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>691366</v>
+        <v>691453</v>
       </c>
       <c r="R28" t="n">
-        <v>6658076</v>
+        <v>6657774</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3676,10 +3676,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126908832</v>
+        <v>126909234</v>
       </c>
       <c r="B29" t="n">
-        <v>100624</v>
+        <v>80077</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3687,34 +3687,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691331</v>
+        <v>691401</v>
       </c>
       <c r="R29" t="n">
-        <v>6657987</v>
+        <v>6657770</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3773,45 +3773,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126909234</v>
+        <v>126909137</v>
       </c>
       <c r="B30" t="n">
-        <v>80077</v>
+        <v>98442</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691401</v>
+        <v>691384</v>
       </c>
       <c r="R30" t="n">
-        <v>6657770</v>
+        <v>6657854</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3870,54 +3879,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126909137</v>
+        <v>126908832</v>
       </c>
       <c r="B31" t="n">
-        <v>98442</v>
+        <v>100624</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691384</v>
+        <v>691331</v>
       </c>
       <c r="R31" t="n">
-        <v>6657854</v>
+        <v>6657987</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3976,10 +3976,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126908066</v>
+        <v>126907198</v>
       </c>
       <c r="B32" t="n">
-        <v>8436</v>
+        <v>97320</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3987,34 +3987,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>691381</v>
+        <v>691387</v>
       </c>
       <c r="R32" t="n">
-        <v>6658051</v>
+        <v>6657944</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4073,10 +4082,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126907198</v>
+        <v>126908052</v>
       </c>
       <c r="B33" t="n">
-        <v>97320</v>
+        <v>100624</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4084,43 +4093,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>691387</v>
+        <v>691381</v>
       </c>
       <c r="R33" t="n">
-        <v>6657944</v>
+        <v>6658051</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126908052</v>
+        <v>126908066</v>
       </c>
       <c r="B34" t="n">
-        <v>100624</v>
+        <v>8436</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4190,21 +4190,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4276,54 +4276,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126908608</v>
+        <v>126906062</v>
       </c>
       <c r="B35" t="n">
-        <v>98442</v>
+        <v>91339</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>691329</v>
+        <v>691432</v>
       </c>
       <c r="R35" t="n">
-        <v>6658013</v>
+        <v>6657786</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4488,45 +4479,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126906062</v>
+        <v>126908608</v>
       </c>
       <c r="B37" t="n">
-        <v>91339</v>
+        <v>98442</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691432</v>
+        <v>691329</v>
       </c>
       <c r="R37" t="n">
-        <v>6657786</v>
+        <v>6658013</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5093,50 +5093,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126908871</v>
+        <v>126909078</v>
       </c>
       <c r="B43" t="n">
-        <v>57654</v>
+        <v>8436</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>691352</v>
+        <v>691347</v>
       </c>
       <c r="R43" t="n">
-        <v>6657981</v>
+        <v>6657905</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5195,10 +5190,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126907354</v>
+        <v>126907007</v>
       </c>
       <c r="B44" t="n">
-        <v>91954</v>
+        <v>8436</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5206,21 +5201,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1339</v>
+        <v>106554</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5230,13 +5225,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691389</v>
+        <v>691368</v>
       </c>
       <c r="R44" t="n">
-        <v>6657968</v>
+        <v>6657895</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5276,21 +5271,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5418,10 +5398,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126909078</v>
+        <v>126907354</v>
       </c>
       <c r="B46" t="n">
-        <v>8436</v>
+        <v>91954</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5429,37 +5409,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106554</v>
+        <v>1339</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691347</v>
+        <v>691389</v>
       </c>
       <c r="R46" t="n">
-        <v>6657905</v>
+        <v>6657968</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5499,6 +5479,21 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5515,45 +5510,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126907007</v>
+        <v>126908871</v>
       </c>
       <c r="B47" t="n">
-        <v>8436</v>
+        <v>57654</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>691368</v>
+        <v>691352</v>
       </c>
       <c r="R47" t="n">
-        <v>6657895</v>
+        <v>6657981</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5612,10 +5612,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126909066</v>
+        <v>126906874</v>
       </c>
       <c r="B48" t="n">
-        <v>5176</v>
+        <v>95795</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5623,37 +5623,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>691337</v>
+        <v>691382</v>
       </c>
       <c r="R48" t="n">
-        <v>6657892</v>
+        <v>6657874</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5806,10 +5806,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126906874</v>
+        <v>126909066</v>
       </c>
       <c r="B50" t="n">
-        <v>95795</v>
+        <v>5176</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5817,37 +5817,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691382</v>
+        <v>691337</v>
       </c>
       <c r="R50" t="n">
-        <v>6657874</v>
+        <v>6657892</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126909033</v>
+        <v>126907301</v>
       </c>
       <c r="B55" t="n">
         <v>98442</v>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6349,17 +6349,17 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>691336</v>
+        <v>691387</v>
       </c>
       <c r="R55" t="n">
-        <v>6657914</v>
+        <v>6657944</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126907301</v>
+        <v>126909033</v>
       </c>
       <c r="B56" t="n">
         <v>98442</v>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6455,17 +6455,17 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>691387</v>
+        <v>691336</v>
       </c>
       <c r="R56" t="n">
-        <v>6657944</v>
+        <v>6657914</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6521,45 +6521,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126908731</v>
+        <v>126907130</v>
       </c>
       <c r="B57" t="n">
-        <v>90862</v>
+        <v>8436</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5747</v>
+        <v>106554</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>691331</v>
+        <v>691416</v>
       </c>
       <c r="R57" t="n">
-        <v>6657987</v>
+        <v>6657910</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6618,10 +6618,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126907540</v>
+        <v>126908731</v>
       </c>
       <c r="B58" t="n">
-        <v>91683</v>
+        <v>90862</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6629,34 +6629,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2062</v>
+        <v>5747</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>691377</v>
+        <v>691331</v>
       </c>
       <c r="R58" t="n">
-        <v>6658022</v>
+        <v>6657987</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6715,48 +6715,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126908472</v>
+        <v>126907540</v>
       </c>
       <c r="B59" t="n">
-        <v>91954</v>
+        <v>91683</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1339</v>
+        <v>2062</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>691283</v>
+        <v>691377</v>
       </c>
       <c r="R59" t="n">
-        <v>6658140</v>
+        <v>6658022</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6812,10 +6812,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126907130</v>
+        <v>126908472</v>
       </c>
       <c r="B60" t="n">
-        <v>8436</v>
+        <v>91954</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6823,37 +6823,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106554</v>
+        <v>1339</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>691416</v>
+        <v>691283</v>
       </c>
       <c r="R60" t="n">
-        <v>6657910</v>
+        <v>6658140</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6909,10 +6909,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126908164</v>
+        <v>126906449</v>
       </c>
       <c r="B61" t="n">
-        <v>5176</v>
+        <v>91290</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6920,37 +6920,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>691373</v>
+        <v>691433</v>
       </c>
       <c r="R61" t="n">
-        <v>6658096</v>
+        <v>6657859</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7006,10 +7006,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126906449</v>
+        <v>126908164</v>
       </c>
       <c r="B62" t="n">
-        <v>91290</v>
+        <v>5176</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7017,37 +7017,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>691433</v>
+        <v>691373</v>
       </c>
       <c r="R62" t="n">
-        <v>6657859</v>
+        <v>6658096</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>

--- a/artfynd/A 30443-2025 artfynd.xlsx
+++ b/artfynd/A 30443-2025 artfynd.xlsx
@@ -3676,45 +3676,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126909234</v>
+        <v>126909137</v>
       </c>
       <c r="B29" t="n">
-        <v>80077</v>
+        <v>98442</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691401</v>
+        <v>691384</v>
       </c>
       <c r="R29" t="n">
-        <v>6657770</v>
+        <v>6657854</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3773,54 +3782,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126909137</v>
+        <v>126908832</v>
       </c>
       <c r="B30" t="n">
-        <v>98442</v>
+        <v>100624</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691384</v>
+        <v>691331</v>
       </c>
       <c r="R30" t="n">
-        <v>6657854</v>
+        <v>6657987</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3879,10 +3879,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126908832</v>
+        <v>126909234</v>
       </c>
       <c r="B31" t="n">
-        <v>100624</v>
+        <v>80077</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3890,34 +3890,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691331</v>
+        <v>691401</v>
       </c>
       <c r="R31" t="n">
-        <v>6657987</v>
+        <v>6657770</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -6009,45 +6009,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126908952</v>
+        <v>126908908</v>
       </c>
       <c r="B52" t="n">
-        <v>8436</v>
+        <v>98442</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>691329</v>
+        <v>691331</v>
       </c>
       <c r="R52" t="n">
-        <v>6657950</v>
+        <v>6657987</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6106,10 +6115,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126907554</v>
+        <v>126908952</v>
       </c>
       <c r="B53" t="n">
-        <v>5196</v>
+        <v>8436</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6117,34 +6126,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>691373</v>
+        <v>691329</v>
       </c>
       <c r="R53" t="n">
-        <v>6658009</v>
+        <v>6657950</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6203,54 +6212,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126908908</v>
+        <v>126907554</v>
       </c>
       <c r="B54" t="n">
-        <v>98442</v>
+        <v>5196</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>691331</v>
+        <v>691373</v>
       </c>
       <c r="R54" t="n">
-        <v>6657987</v>
+        <v>6658009</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 30443-2025 artfynd.xlsx
+++ b/artfynd/A 30443-2025 artfynd.xlsx
@@ -1864,7 +1864,7 @@
         <v>126908435</v>
       </c>
       <c r="B11" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>126909177</v>
       </c>
       <c r="B12" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>126907068</v>
       </c>
       <c r="B13" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>126907789</v>
       </c>
       <c r="B15" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2364,10 +2364,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126907984</v>
+        <v>126908037</v>
       </c>
       <c r="B16" t="n">
-        <v>95795</v>
+        <v>95892</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,37 +2375,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691394</v>
+        <v>691381</v>
       </c>
       <c r="R16" t="n">
-        <v>6658034</v>
+        <v>6658051</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2461,57 +2470,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126908037</v>
+        <v>126908154</v>
       </c>
       <c r="B17" t="n">
-        <v>95891</v>
+        <v>91326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>210</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691381</v>
+        <v>691373</v>
       </c>
       <c r="R17" t="n">
-        <v>6658051</v>
+        <v>6658096</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2567,32 +2567,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126908154</v>
+        <v>126907984</v>
       </c>
       <c r="B18" t="n">
-        <v>91325</v>
+        <v>95796</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2602,10 +2602,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691373</v>
+        <v>691394</v>
       </c>
       <c r="R18" t="n">
-        <v>6658096</v>
+        <v>6658034</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2667,7 +2667,7 @@
         <v>126906047</v>
       </c>
       <c r="B19" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,45 +2761,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126908926</v>
+        <v>126907030</v>
       </c>
       <c r="B20" t="n">
-        <v>8436</v>
+        <v>98443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691339</v>
+        <v>691371</v>
       </c>
       <c r="R20" t="n">
-        <v>6657957</v>
+        <v>6657926</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2858,54 +2867,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126907030</v>
+        <v>126908926</v>
       </c>
       <c r="B21" t="n">
-        <v>98442</v>
+        <v>8436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691371</v>
+        <v>691339</v>
       </c>
       <c r="R21" t="n">
-        <v>6657926</v>
+        <v>6657957</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3064,7 +3064,7 @@
         <v>126909047</v>
       </c>
       <c r="B23" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,32 +3167,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126905851</v>
+        <v>126907497</v>
       </c>
       <c r="B24" t="n">
-        <v>91954</v>
+        <v>91326</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691458</v>
+        <v>691377</v>
       </c>
       <c r="R24" t="n">
-        <v>6657753</v>
+        <v>6658022</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3248,21 +3248,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3279,32 +3264,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126907497</v>
+        <v>126905851</v>
       </c>
       <c r="B25" t="n">
-        <v>91325</v>
+        <v>91955</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3314,10 +3299,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691377</v>
+        <v>691458</v>
       </c>
       <c r="R25" t="n">
-        <v>6658022</v>
+        <v>6657753</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3360,6 +3345,21 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3376,54 +3376,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126908119</v>
+        <v>126905916</v>
       </c>
       <c r="B26" t="n">
-        <v>98442</v>
+        <v>85036</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1971</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor sotdyna</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Camarops polysperma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Mont.) J.H.Mill.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691366</v>
+        <v>691453</v>
       </c>
       <c r="R26" t="n">
-        <v>6658076</v>
+        <v>6657774</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3579,45 +3570,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126905916</v>
+        <v>126908119</v>
       </c>
       <c r="B28" t="n">
-        <v>85036</v>
+        <v>98443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1971</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stor sotdyna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Camarops polysperma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Mont.) J.H.Mill.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>691453</v>
+        <v>691366</v>
       </c>
       <c r="R28" t="n">
-        <v>6657774</v>
+        <v>6658076</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3679,7 +3679,7 @@
         <v>126909137</v>
       </c>
       <c r="B29" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3782,10 +3782,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126908832</v>
+        <v>126909234</v>
       </c>
       <c r="B30" t="n">
-        <v>100624</v>
+        <v>80077</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3793,34 +3793,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691331</v>
+        <v>691401</v>
       </c>
       <c r="R30" t="n">
-        <v>6657987</v>
+        <v>6657770</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3879,10 +3879,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126909234</v>
+        <v>126908832</v>
       </c>
       <c r="B31" t="n">
-        <v>80077</v>
+        <v>100625</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3890,34 +3890,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691401</v>
+        <v>691331</v>
       </c>
       <c r="R31" t="n">
-        <v>6657770</v>
+        <v>6657987</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3976,10 +3976,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126907198</v>
+        <v>126908052</v>
       </c>
       <c r="B32" t="n">
-        <v>97320</v>
+        <v>100625</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3987,43 +3987,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>691387</v>
+        <v>691381</v>
       </c>
       <c r="R32" t="n">
-        <v>6657944</v>
+        <v>6658051</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4082,10 +4073,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126908052</v>
+        <v>126908066</v>
       </c>
       <c r="B33" t="n">
-        <v>100624</v>
+        <v>8436</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4093,21 +4084,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4179,10 +4170,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126908066</v>
+        <v>126907198</v>
       </c>
       <c r="B34" t="n">
-        <v>8436</v>
+        <v>97321</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4190,34 +4181,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>691381</v>
+        <v>691387</v>
       </c>
       <c r="R34" t="n">
-        <v>6658051</v>
+        <v>6657944</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4276,48 +4276,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126906062</v>
+        <v>126906629</v>
       </c>
       <c r="B35" t="n">
-        <v>91339</v>
+        <v>105478</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1204</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>691432</v>
+        <v>691376</v>
       </c>
       <c r="R35" t="n">
-        <v>6657786</v>
+        <v>6657865</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4373,37 +4382,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126906629</v>
+        <v>126908608</v>
       </c>
       <c r="B36" t="n">
-        <v>105477</v>
+        <v>98443</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4413,17 +4422,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691376</v>
+        <v>691329</v>
       </c>
       <c r="R36" t="n">
-        <v>6657865</v>
+        <v>6658013</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4479,54 +4488,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126908608</v>
+        <v>126906062</v>
       </c>
       <c r="B37" t="n">
-        <v>98442</v>
+        <v>91340</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691329</v>
+        <v>691432</v>
       </c>
       <c r="R37" t="n">
-        <v>6658013</v>
+        <v>6657786</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4585,45 +4585,54 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126907654</v>
+        <v>126907715</v>
       </c>
       <c r="B38" t="n">
-        <v>5176</v>
+        <v>98443</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691381</v>
+        <v>691363</v>
       </c>
       <c r="R38" t="n">
-        <v>6658039</v>
+        <v>6658060</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4682,7 +4691,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126908912</v>
+        <v>126907654</v>
       </c>
       <c r="B39" t="n">
         <v>5176</v>
@@ -4713,17 +4722,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691331</v>
+        <v>691381</v>
       </c>
       <c r="R39" t="n">
-        <v>6657987</v>
+        <v>6658039</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4779,57 +4788,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126907715</v>
+        <v>126908912</v>
       </c>
       <c r="B40" t="n">
-        <v>98442</v>
+        <v>5176</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>691363</v>
+        <v>691331</v>
       </c>
       <c r="R40" t="n">
-        <v>6658060</v>
+        <v>6657987</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>126907755</v>
       </c>
       <c r="B42" t="n">
-        <v>105477</v>
+        <v>105478</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5093,10 +5093,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126909078</v>
+        <v>126907354</v>
       </c>
       <c r="B43" t="n">
-        <v>8436</v>
+        <v>91955</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5104,37 +5104,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106554</v>
+        <v>1339</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>691347</v>
+        <v>691389</v>
       </c>
       <c r="R43" t="n">
-        <v>6657905</v>
+        <v>6657968</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5174,6 +5174,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5190,10 +5205,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126907007</v>
+        <v>126908462</v>
       </c>
       <c r="B44" t="n">
-        <v>8436</v>
+        <v>105478</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5201,37 +5216,46 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106554</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691368</v>
+        <v>691296</v>
       </c>
       <c r="R44" t="n">
-        <v>6657895</v>
+        <v>6658183</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5261,6 +5285,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Cirka</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5287,42 +5316,38 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126908462</v>
+        <v>126908871</v>
       </c>
       <c r="B45" t="n">
-        <v>105477</v>
+        <v>57654</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5331,13 +5356,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691296</v>
+        <v>691352</v>
       </c>
       <c r="R45" t="n">
-        <v>6658183</v>
+        <v>6657981</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5367,11 +5392,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Cirka</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5398,10 +5418,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126907354</v>
+        <v>126909078</v>
       </c>
       <c r="B46" t="n">
-        <v>91954</v>
+        <v>8436</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5409,37 +5429,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1339</v>
+        <v>106554</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691389</v>
+        <v>691347</v>
       </c>
       <c r="R46" t="n">
-        <v>6657968</v>
+        <v>6657905</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5479,21 +5499,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5510,50 +5515,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126908871</v>
+        <v>126907007</v>
       </c>
       <c r="B47" t="n">
-        <v>57654</v>
+        <v>8436</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>691352</v>
+        <v>691368</v>
       </c>
       <c r="R47" t="n">
-        <v>6657981</v>
+        <v>6657895</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5615,7 +5615,7 @@
         <v>126906874</v>
       </c>
       <c r="B48" t="n">
-        <v>95795</v>
+        <v>95796</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>126908159</v>
       </c>
       <c r="B49" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>126906755</v>
       </c>
       <c r="B51" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>126908908</v>
       </c>
       <c r="B52" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6309,10 +6309,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126907301</v>
+        <v>126909033</v>
       </c>
       <c r="B55" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6349,17 +6349,17 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>691387</v>
+        <v>691336</v>
       </c>
       <c r="R55" t="n">
-        <v>6657944</v>
+        <v>6657914</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6415,10 +6415,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126909033</v>
+        <v>126907301</v>
       </c>
       <c r="B56" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6455,17 +6455,17 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>691336</v>
+        <v>691387</v>
       </c>
       <c r="R56" t="n">
-        <v>6657914</v>
+        <v>6657944</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6521,32 +6521,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126907130</v>
+        <v>126907540</v>
       </c>
       <c r="B57" t="n">
-        <v>8436</v>
+        <v>91684</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106554</v>
+        <v>2062</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6556,10 +6556,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>691416</v>
+        <v>691377</v>
       </c>
       <c r="R57" t="n">
-        <v>6657910</v>
+        <v>6658022</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6618,32 +6618,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126908731</v>
+        <v>126908472</v>
       </c>
       <c r="B58" t="n">
-        <v>90862</v>
+        <v>91955</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5747</v>
+        <v>1339</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6653,13 +6653,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>691331</v>
+        <v>691283</v>
       </c>
       <c r="R58" t="n">
-        <v>6657987</v>
+        <v>6658140</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6715,32 +6715,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126907540</v>
+        <v>126907130</v>
       </c>
       <c r="B59" t="n">
-        <v>91683</v>
+        <v>8436</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2062</v>
+        <v>106554</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6750,10 +6750,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>691377</v>
+        <v>691416</v>
       </c>
       <c r="R59" t="n">
-        <v>6658022</v>
+        <v>6657910</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6812,32 +6812,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126908472</v>
+        <v>126908731</v>
       </c>
       <c r="B60" t="n">
-        <v>91954</v>
+        <v>90863</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1339</v>
+        <v>5747</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>691283</v>
+        <v>691331</v>
       </c>
       <c r="R60" t="n">
-        <v>6658140</v>
+        <v>6657987</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>126906449</v>
       </c>
       <c r="B61" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>126951967</v>
       </c>
       <c r="B63" t="n">
-        <v>105296</v>
+        <v>105297</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 30443-2025 artfynd.xlsx
+++ b/artfynd/A 30443-2025 artfynd.xlsx
@@ -2364,54 +2364,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126908037</v>
+        <v>126907030</v>
       </c>
       <c r="B16" t="n">
-        <v>95892</v>
+        <v>98443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691381</v>
+        <v>691371</v>
       </c>
       <c r="R16" t="n">
-        <v>6658051</v>
+        <v>6657926</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2470,48 +2470,57 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126908154</v>
+        <v>126908037</v>
       </c>
       <c r="B17" t="n">
-        <v>91326</v>
+        <v>95892</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691373</v>
+        <v>691381</v>
       </c>
       <c r="R17" t="n">
-        <v>6658096</v>
+        <v>6658051</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2567,32 +2576,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126907984</v>
+        <v>126908154</v>
       </c>
       <c r="B18" t="n">
-        <v>95796</v>
+        <v>91326</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2602,10 +2611,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691394</v>
+        <v>691373</v>
       </c>
       <c r="R18" t="n">
-        <v>6658034</v>
+        <v>6658096</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2664,45 +2673,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126906047</v>
+        <v>126907984</v>
       </c>
       <c r="B19" t="n">
-        <v>91326</v>
+        <v>95796</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691432</v>
+        <v>691394</v>
       </c>
       <c r="R19" t="n">
-        <v>6657786</v>
+        <v>6658034</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2761,57 +2770,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126907030</v>
+        <v>126906047</v>
       </c>
       <c r="B20" t="n">
-        <v>98443</v>
+        <v>91326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691371</v>
+        <v>691432</v>
       </c>
       <c r="R20" t="n">
-        <v>6657926</v>
+        <v>6657786</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3976,10 +3976,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126908052</v>
+        <v>126908066</v>
       </c>
       <c r="B32" t="n">
-        <v>100625</v>
+        <v>8436</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3987,21 +3987,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4073,10 +4073,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126908066</v>
+        <v>126907198</v>
       </c>
       <c r="B33" t="n">
-        <v>8436</v>
+        <v>97321</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4084,34 +4084,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>691381</v>
+        <v>691387</v>
       </c>
       <c r="R33" t="n">
-        <v>6658051</v>
+        <v>6657944</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4170,10 +4179,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126907198</v>
+        <v>126908052</v>
       </c>
       <c r="B34" t="n">
-        <v>97321</v>
+        <v>100625</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4181,43 +4190,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>691387</v>
+        <v>691381</v>
       </c>
       <c r="R34" t="n">
-        <v>6657944</v>
+        <v>6658051</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4276,57 +4276,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126906629</v>
+        <v>126906062</v>
       </c>
       <c r="B35" t="n">
-        <v>105478</v>
+        <v>91340</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>1204</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>691376</v>
+        <v>691432</v>
       </c>
       <c r="R35" t="n">
-        <v>6657865</v>
+        <v>6657786</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4382,37 +4373,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126908608</v>
+        <v>126906629</v>
       </c>
       <c r="B36" t="n">
-        <v>98443</v>
+        <v>105478</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4422,17 +4413,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691329</v>
+        <v>691376</v>
       </c>
       <c r="R36" t="n">
-        <v>6658013</v>
+        <v>6657865</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4488,45 +4479,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126906062</v>
+        <v>126908608</v>
       </c>
       <c r="B37" t="n">
-        <v>91340</v>
+        <v>98443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691432</v>
+        <v>691329</v>
       </c>
       <c r="R37" t="n">
-        <v>6657786</v>
+        <v>6658013</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5205,10 +5205,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126908462</v>
+        <v>126909078</v>
       </c>
       <c r="B44" t="n">
-        <v>105478</v>
+        <v>8436</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5216,46 +5216,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221144</v>
+        <v>106554</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691296</v>
+        <v>691347</v>
       </c>
       <c r="R44" t="n">
-        <v>6658183</v>
+        <v>6657905</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5285,11 +5276,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Cirka</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5316,50 +5302,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126908871</v>
+        <v>126907007</v>
       </c>
       <c r="B45" t="n">
-        <v>57654</v>
+        <v>8436</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691352</v>
+        <v>691368</v>
       </c>
       <c r="R45" t="n">
-        <v>6657981</v>
+        <v>6657895</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5418,10 +5399,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126909078</v>
+        <v>126908462</v>
       </c>
       <c r="B46" t="n">
-        <v>8436</v>
+        <v>105478</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5429,37 +5410,46 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106554</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691347</v>
+        <v>691296</v>
       </c>
       <c r="R46" t="n">
-        <v>6657905</v>
+        <v>6658183</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5489,6 +5479,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Cirka</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5515,45 +5510,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126907007</v>
+        <v>126908871</v>
       </c>
       <c r="B47" t="n">
-        <v>8436</v>
+        <v>57654</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>691368</v>
+        <v>691352</v>
       </c>
       <c r="R47" t="n">
-        <v>6657895</v>
+        <v>6657981</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5612,10 +5612,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126906874</v>
+        <v>126909066</v>
       </c>
       <c r="B48" t="n">
-        <v>95796</v>
+        <v>5176</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5623,37 +5623,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>691382</v>
+        <v>691337</v>
       </c>
       <c r="R48" t="n">
-        <v>6657874</v>
+        <v>6657892</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5709,48 +5709,57 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126908159</v>
+        <v>126906755</v>
       </c>
       <c r="B49" t="n">
-        <v>91291</v>
+        <v>98443</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>691373</v>
+        <v>691376</v>
       </c>
       <c r="R49" t="n">
-        <v>6658096</v>
+        <v>6657865</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5806,10 +5815,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126909066</v>
+        <v>126906874</v>
       </c>
       <c r="B50" t="n">
-        <v>5176</v>
+        <v>95796</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5817,37 +5826,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691337</v>
+        <v>691382</v>
       </c>
       <c r="R50" t="n">
-        <v>6657892</v>
+        <v>6657874</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5903,57 +5912,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126906755</v>
+        <v>126908159</v>
       </c>
       <c r="B51" t="n">
-        <v>98443</v>
+        <v>91291</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>691376</v>
+        <v>691373</v>
       </c>
       <c r="R51" t="n">
-        <v>6657865</v>
+        <v>6658096</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>

--- a/artfynd/A 30443-2025 artfynd.xlsx
+++ b/artfynd/A 30443-2025 artfynd.xlsx
@@ -2364,54 +2364,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126907030</v>
+        <v>126908037</v>
       </c>
       <c r="B16" t="n">
-        <v>98443</v>
+        <v>95892</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691371</v>
+        <v>691381</v>
       </c>
       <c r="R16" t="n">
-        <v>6657926</v>
+        <v>6658051</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2470,57 +2470,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126908037</v>
+        <v>126908154</v>
       </c>
       <c r="B17" t="n">
-        <v>95892</v>
+        <v>91326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>210</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691381</v>
+        <v>691373</v>
       </c>
       <c r="R17" t="n">
-        <v>6658051</v>
+        <v>6658096</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2576,7 +2567,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126908154</v>
+        <v>126906047</v>
       </c>
       <c r="B18" t="n">
         <v>91326</v>
@@ -2607,14 +2598,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691373</v>
+        <v>691432</v>
       </c>
       <c r="R18" t="n">
-        <v>6658096</v>
+        <v>6657786</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2770,48 +2761,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126906047</v>
+        <v>126908926</v>
       </c>
       <c r="B20" t="n">
-        <v>91326</v>
+        <v>8436</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691432</v>
+        <v>691339</v>
       </c>
       <c r="R20" t="n">
-        <v>6657786</v>
+        <v>6657957</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2867,45 +2858,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126908926</v>
+        <v>126907030</v>
       </c>
       <c r="B21" t="n">
-        <v>8436</v>
+        <v>98443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691339</v>
+        <v>691371</v>
       </c>
       <c r="R21" t="n">
-        <v>6657957</v>
+        <v>6657926</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2964,45 +2964,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126906093</v>
+        <v>126909047</v>
       </c>
       <c r="B22" t="n">
-        <v>5176</v>
+        <v>98443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691432</v>
+        <v>691329</v>
       </c>
       <c r="R22" t="n">
-        <v>6657786</v>
+        <v>6657950</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3061,54 +3070,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126909047</v>
+        <v>126906093</v>
       </c>
       <c r="B23" t="n">
-        <v>98443</v>
+        <v>5176</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691329</v>
+        <v>691432</v>
       </c>
       <c r="R23" t="n">
-        <v>6657950</v>
+        <v>6657786</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3676,54 +3676,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126909137</v>
+        <v>126908832</v>
       </c>
       <c r="B29" t="n">
-        <v>98443</v>
+        <v>100625</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691384</v>
+        <v>691331</v>
       </c>
       <c r="R29" t="n">
-        <v>6657854</v>
+        <v>6657987</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3879,45 +3870,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126908832</v>
+        <v>126909137</v>
       </c>
       <c r="B31" t="n">
-        <v>100625</v>
+        <v>98443</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691331</v>
+        <v>691384</v>
       </c>
       <c r="R31" t="n">
-        <v>6657987</v>
+        <v>6657854</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4373,37 +4373,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126906629</v>
+        <v>126908608</v>
       </c>
       <c r="B36" t="n">
-        <v>105478</v>
+        <v>98443</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4413,17 +4413,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691376</v>
+        <v>691329</v>
       </c>
       <c r="R36" t="n">
-        <v>6657865</v>
+        <v>6658013</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4479,37 +4479,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126908608</v>
+        <v>126906629</v>
       </c>
       <c r="B37" t="n">
-        <v>98443</v>
+        <v>105478</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4519,17 +4519,17 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691329</v>
+        <v>691376</v>
       </c>
       <c r="R37" t="n">
-        <v>6658013</v>
+        <v>6657865</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4585,54 +4585,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126907715</v>
+        <v>126907654</v>
       </c>
       <c r="B38" t="n">
-        <v>98443</v>
+        <v>5176</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691363</v>
+        <v>691381</v>
       </c>
       <c r="R38" t="n">
-        <v>6658060</v>
+        <v>6658039</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4691,7 +4682,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126907654</v>
+        <v>126908912</v>
       </c>
       <c r="B39" t="n">
         <v>5176</v>
@@ -4722,17 +4713,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691381</v>
+        <v>691331</v>
       </c>
       <c r="R39" t="n">
-        <v>6658039</v>
+        <v>6657987</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4788,48 +4779,57 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126908912</v>
+        <v>126907715</v>
       </c>
       <c r="B40" t="n">
-        <v>5176</v>
+        <v>98443</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>691331</v>
+        <v>691363</v>
       </c>
       <c r="R40" t="n">
-        <v>6657987</v>
+        <v>6658060</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5399,42 +5399,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126908462</v>
+        <v>126908871</v>
       </c>
       <c r="B46" t="n">
-        <v>105478</v>
+        <v>57654</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5443,13 +5439,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691296</v>
+        <v>691352</v>
       </c>
       <c r="R46" t="n">
-        <v>6658183</v>
+        <v>6657981</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5479,11 +5475,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Cirka</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5510,38 +5501,42 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126908871</v>
+        <v>126908462</v>
       </c>
       <c r="B47" t="n">
-        <v>57654</v>
+        <v>105478</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5550,13 +5545,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>691352</v>
+        <v>691296</v>
       </c>
       <c r="R47" t="n">
-        <v>6657981</v>
+        <v>6658183</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5586,6 +5581,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Cirka</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5612,10 +5612,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126909066</v>
+        <v>126906874</v>
       </c>
       <c r="B48" t="n">
-        <v>5176</v>
+        <v>95796</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5623,37 +5623,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>691337</v>
+        <v>691382</v>
       </c>
       <c r="R48" t="n">
-        <v>6657892</v>
+        <v>6657874</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5709,57 +5709,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126906755</v>
+        <v>126908159</v>
       </c>
       <c r="B49" t="n">
-        <v>98443</v>
+        <v>91291</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>691376</v>
+        <v>691373</v>
       </c>
       <c r="R49" t="n">
-        <v>6657865</v>
+        <v>6658096</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5815,48 +5806,57 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126906874</v>
+        <v>126906755</v>
       </c>
       <c r="B50" t="n">
-        <v>95796</v>
+        <v>98443</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2818</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691382</v>
+        <v>691376</v>
       </c>
       <c r="R50" t="n">
-        <v>6657874</v>
+        <v>6657865</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5912,10 +5912,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126908159</v>
+        <v>126909066</v>
       </c>
       <c r="B51" t="n">
-        <v>91291</v>
+        <v>5176</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5923,21 +5923,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5947,13 +5947,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>691373</v>
+        <v>691337</v>
       </c>
       <c r="R51" t="n">
-        <v>6658096</v>
+        <v>6657892</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6009,54 +6009,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126908908</v>
+        <v>126907554</v>
       </c>
       <c r="B52" t="n">
-        <v>98443</v>
+        <v>5196</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>691331</v>
+        <v>691373</v>
       </c>
       <c r="R52" t="n">
-        <v>6657987</v>
+        <v>6658009</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6212,45 +6203,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126907554</v>
+        <v>126908908</v>
       </c>
       <c r="B54" t="n">
-        <v>5196</v>
+        <v>98443</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>691373</v>
+        <v>691331</v>
       </c>
       <c r="R54" t="n">
-        <v>6658009</v>
+        <v>6657987</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6309,7 +6309,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126909033</v>
+        <v>126907301</v>
       </c>
       <c r="B55" t="n">
         <v>98443</v>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6349,17 +6349,17 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>691336</v>
+        <v>691387</v>
       </c>
       <c r="R55" t="n">
-        <v>6657914</v>
+        <v>6657944</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126907301</v>
+        <v>126909033</v>
       </c>
       <c r="B56" t="n">
         <v>98443</v>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6455,17 +6455,17 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>691387</v>
+        <v>691336</v>
       </c>
       <c r="R56" t="n">
-        <v>6657944</v>
+        <v>6657914</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6521,48 +6521,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126907540</v>
+        <v>126908472</v>
       </c>
       <c r="B57" t="n">
-        <v>91684</v>
+        <v>91955</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2062</v>
+        <v>1339</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>691377</v>
+        <v>691283</v>
       </c>
       <c r="R57" t="n">
-        <v>6658022</v>
+        <v>6658140</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6618,48 +6618,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126908472</v>
+        <v>126907540</v>
       </c>
       <c r="B58" t="n">
-        <v>91955</v>
+        <v>91684</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1339</v>
+        <v>2062</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>691283</v>
+        <v>691377</v>
       </c>
       <c r="R58" t="n">
-        <v>6658140</v>
+        <v>6658022</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>

--- a/artfynd/A 30443-2025 artfynd.xlsx
+++ b/artfynd/A 30443-2025 artfynd.xlsx
@@ -2964,54 +2964,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126909047</v>
+        <v>126906093</v>
       </c>
       <c r="B22" t="n">
-        <v>98443</v>
+        <v>5176</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691329</v>
+        <v>691432</v>
       </c>
       <c r="R22" t="n">
-        <v>6657950</v>
+        <v>6657786</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3070,45 +3061,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126906093</v>
+        <v>126909047</v>
       </c>
       <c r="B23" t="n">
-        <v>5176</v>
+        <v>98443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691432</v>
+        <v>691329</v>
       </c>
       <c r="R23" t="n">
-        <v>6657786</v>
+        <v>6657950</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3676,10 +3676,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126908832</v>
+        <v>126909234</v>
       </c>
       <c r="B29" t="n">
-        <v>100625</v>
+        <v>80077</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3687,34 +3687,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691331</v>
+        <v>691401</v>
       </c>
       <c r="R29" t="n">
-        <v>6657987</v>
+        <v>6657770</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126909234</v>
+        <v>126908832</v>
       </c>
       <c r="B30" t="n">
-        <v>80077</v>
+        <v>100625</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3784,34 +3784,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691401</v>
+        <v>691331</v>
       </c>
       <c r="R30" t="n">
-        <v>6657770</v>
+        <v>6657987</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4073,10 +4073,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126907198</v>
+        <v>126908052</v>
       </c>
       <c r="B33" t="n">
-        <v>97321</v>
+        <v>100625</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4084,43 +4084,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>691387</v>
+        <v>691381</v>
       </c>
       <c r="R33" t="n">
-        <v>6657944</v>
+        <v>6658051</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4179,10 +4170,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126908052</v>
+        <v>126907198</v>
       </c>
       <c r="B34" t="n">
-        <v>100625</v>
+        <v>97321</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4190,34 +4181,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>691381</v>
+        <v>691387</v>
       </c>
       <c r="R34" t="n">
-        <v>6658051</v>
+        <v>6657944</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4585,45 +4585,54 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126907654</v>
+        <v>126907715</v>
       </c>
       <c r="B38" t="n">
-        <v>5176</v>
+        <v>98443</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691381</v>
+        <v>691363</v>
       </c>
       <c r="R38" t="n">
-        <v>6658039</v>
+        <v>6658060</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4682,7 +4691,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126908912</v>
+        <v>126907654</v>
       </c>
       <c r="B39" t="n">
         <v>5176</v>
@@ -4713,17 +4722,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691331</v>
+        <v>691381</v>
       </c>
       <c r="R39" t="n">
-        <v>6657987</v>
+        <v>6658039</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4779,57 +4788,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126907715</v>
+        <v>126908912</v>
       </c>
       <c r="B40" t="n">
-        <v>98443</v>
+        <v>5176</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>691363</v>
+        <v>691331</v>
       </c>
       <c r="R40" t="n">
-        <v>6658060</v>
+        <v>6657987</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>

--- a/artfynd/A 30443-2025 artfynd.xlsx
+++ b/artfynd/A 30443-2025 artfynd.xlsx
@@ -2364,10 +2364,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126908037</v>
+        <v>126907984</v>
       </c>
       <c r="B16" t="n">
-        <v>95892</v>
+        <v>95796</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,46 +2375,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691381</v>
+        <v>691394</v>
       </c>
       <c r="R16" t="n">
-        <v>6658051</v>
+        <v>6658034</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2470,48 +2461,57 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126908154</v>
+        <v>126908037</v>
       </c>
       <c r="B17" t="n">
-        <v>91326</v>
+        <v>95892</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691373</v>
+        <v>691381</v>
       </c>
       <c r="R17" t="n">
-        <v>6658096</v>
+        <v>6658051</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126906047</v>
+        <v>126908154</v>
       </c>
       <c r="B18" t="n">
         <v>91326</v>
@@ -2598,14 +2598,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691432</v>
+        <v>691373</v>
       </c>
       <c r="R18" t="n">
-        <v>6657786</v>
+        <v>6658096</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2664,45 +2664,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126907984</v>
+        <v>126906047</v>
       </c>
       <c r="B19" t="n">
-        <v>95796</v>
+        <v>91326</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691394</v>
+        <v>691432</v>
       </c>
       <c r="R19" t="n">
-        <v>6658034</v>
+        <v>6657786</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2964,45 +2964,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126906093</v>
+        <v>126909047</v>
       </c>
       <c r="B22" t="n">
-        <v>5176</v>
+        <v>98443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691432</v>
+        <v>691329</v>
       </c>
       <c r="R22" t="n">
-        <v>6657786</v>
+        <v>6657950</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3061,54 +3070,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126909047</v>
+        <v>126906093</v>
       </c>
       <c r="B23" t="n">
-        <v>98443</v>
+        <v>5176</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691329</v>
+        <v>691432</v>
       </c>
       <c r="R23" t="n">
-        <v>6657950</v>
+        <v>6657786</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -4073,10 +4073,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126908052</v>
+        <v>126907198</v>
       </c>
       <c r="B33" t="n">
-        <v>100625</v>
+        <v>97321</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4084,34 +4084,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>691381</v>
+        <v>691387</v>
       </c>
       <c r="R33" t="n">
-        <v>6658051</v>
+        <v>6657944</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4170,10 +4179,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126907198</v>
+        <v>126908052</v>
       </c>
       <c r="B34" t="n">
-        <v>97321</v>
+        <v>100625</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4181,43 +4190,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>691387</v>
+        <v>691381</v>
       </c>
       <c r="R34" t="n">
-        <v>6657944</v>
+        <v>6658051</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4585,54 +4585,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126907715</v>
+        <v>126907654</v>
       </c>
       <c r="B38" t="n">
-        <v>98443</v>
+        <v>5176</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691363</v>
+        <v>691381</v>
       </c>
       <c r="R38" t="n">
-        <v>6658060</v>
+        <v>6658039</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4691,7 +4682,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126907654</v>
+        <v>126908912</v>
       </c>
       <c r="B39" t="n">
         <v>5176</v>
@@ -4722,17 +4713,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691381</v>
+        <v>691331</v>
       </c>
       <c r="R39" t="n">
-        <v>6658039</v>
+        <v>6657987</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4788,48 +4779,57 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126908912</v>
+        <v>126907715</v>
       </c>
       <c r="B40" t="n">
-        <v>5176</v>
+        <v>98443</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>691331</v>
+        <v>691363</v>
       </c>
       <c r="R40" t="n">
-        <v>6657987</v>
+        <v>6658060</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5205,45 +5205,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126909078</v>
+        <v>126908871</v>
       </c>
       <c r="B44" t="n">
-        <v>8436</v>
+        <v>57654</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691347</v>
+        <v>691352</v>
       </c>
       <c r="R44" t="n">
-        <v>6657905</v>
+        <v>6657981</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5302,7 +5307,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126907007</v>
+        <v>126909078</v>
       </c>
       <c r="B45" t="n">
         <v>8436</v>
@@ -5333,14 +5338,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691368</v>
+        <v>691347</v>
       </c>
       <c r="R45" t="n">
-        <v>6657895</v>
+        <v>6657905</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5399,50 +5404,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126908871</v>
+        <v>126907007</v>
       </c>
       <c r="B46" t="n">
-        <v>57654</v>
+        <v>8436</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691352</v>
+        <v>691368</v>
       </c>
       <c r="R46" t="n">
-        <v>6657981</v>
+        <v>6657895</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5612,10 +5612,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126906874</v>
+        <v>126909066</v>
       </c>
       <c r="B48" t="n">
-        <v>95796</v>
+        <v>5176</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5623,37 +5623,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>691382</v>
+        <v>691337</v>
       </c>
       <c r="R48" t="n">
-        <v>6657874</v>
+        <v>6657892</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5709,48 +5709,57 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126908159</v>
+        <v>126906755</v>
       </c>
       <c r="B49" t="n">
-        <v>91291</v>
+        <v>98443</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>691373</v>
+        <v>691376</v>
       </c>
       <c r="R49" t="n">
-        <v>6658096</v>
+        <v>6657865</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5806,57 +5815,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126906755</v>
+        <v>126906874</v>
       </c>
       <c r="B50" t="n">
-        <v>98443</v>
+        <v>95796</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>2818</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691376</v>
+        <v>691382</v>
       </c>
       <c r="R50" t="n">
-        <v>6657865</v>
+        <v>6657874</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5912,10 +5912,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126909066</v>
+        <v>126908159</v>
       </c>
       <c r="B51" t="n">
-        <v>5176</v>
+        <v>91291</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5923,21 +5923,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5947,13 +5947,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>691337</v>
+        <v>691373</v>
       </c>
       <c r="R51" t="n">
-        <v>6657892</v>
+        <v>6658096</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6009,10 +6009,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126907554</v>
+        <v>126908952</v>
       </c>
       <c r="B52" t="n">
-        <v>5196</v>
+        <v>8436</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6020,34 +6020,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>691373</v>
+        <v>691329</v>
       </c>
       <c r="R52" t="n">
-        <v>6658009</v>
+        <v>6657950</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6106,10 +6106,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126908952</v>
+        <v>126907554</v>
       </c>
       <c r="B53" t="n">
-        <v>8436</v>
+        <v>5196</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6117,34 +6117,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>691329</v>
+        <v>691373</v>
       </c>
       <c r="R53" t="n">
-        <v>6657950</v>
+        <v>6658009</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6715,45 +6715,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126907130</v>
+        <v>126908731</v>
       </c>
       <c r="B59" t="n">
-        <v>8436</v>
+        <v>90863</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106554</v>
+        <v>5747</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>691416</v>
+        <v>691331</v>
       </c>
       <c r="R59" t="n">
-        <v>6657910</v>
+        <v>6657987</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6812,45 +6812,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126908731</v>
+        <v>126907130</v>
       </c>
       <c r="B60" t="n">
-        <v>90863</v>
+        <v>8436</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5747</v>
+        <v>106554</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>691331</v>
+        <v>691416</v>
       </c>
       <c r="R60" t="n">
-        <v>6657987</v>
+        <v>6657910</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>

--- a/artfynd/A 30443-2025 artfynd.xlsx
+++ b/artfynd/A 30443-2025 artfynd.xlsx
@@ -1864,7 +1864,7 @@
         <v>126908435</v>
       </c>
       <c r="B11" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>126909177</v>
       </c>
       <c r="B12" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>126907068</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>126906462</v>
       </c>
       <c r="B14" t="n">
-        <v>5176</v>
+        <v>5177</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>126907789</v>
       </c>
       <c r="B15" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2364,32 +2364,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126907984</v>
+        <v>126908154</v>
       </c>
       <c r="B16" t="n">
-        <v>95796</v>
+        <v>91330</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691394</v>
+        <v>691373</v>
       </c>
       <c r="R16" t="n">
-        <v>6658034</v>
+        <v>6658096</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2464,7 +2464,7 @@
         <v>126908037</v>
       </c>
       <c r="B17" t="n">
-        <v>95892</v>
+        <v>95896</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2567,10 +2567,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126908154</v>
+        <v>126906047</v>
       </c>
       <c r="B18" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,14 +2598,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691373</v>
+        <v>691432</v>
       </c>
       <c r="R18" t="n">
-        <v>6658096</v>
+        <v>6657786</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2664,48 +2664,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126906047</v>
+        <v>126908926</v>
       </c>
       <c r="B19" t="n">
-        <v>91326</v>
+        <v>8439</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691432</v>
+        <v>691339</v>
       </c>
       <c r="R19" t="n">
-        <v>6657786</v>
+        <v>6657957</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126908926</v>
+        <v>126907984</v>
       </c>
       <c r="B20" t="n">
-        <v>8436</v>
+        <v>95800</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2772,21 +2772,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>2818</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2796,13 +2796,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691339</v>
+        <v>691394</v>
       </c>
       <c r="R20" t="n">
-        <v>6657957</v>
+        <v>6658034</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>126907030</v>
       </c>
       <c r="B21" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,54 +2964,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126909047</v>
+        <v>126906093</v>
       </c>
       <c r="B22" t="n">
-        <v>98443</v>
+        <v>5177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691329</v>
+        <v>691432</v>
       </c>
       <c r="R22" t="n">
-        <v>6657950</v>
+        <v>6657786</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3070,45 +3061,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126906093</v>
+        <v>126909047</v>
       </c>
       <c r="B23" t="n">
-        <v>5176</v>
+        <v>98447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691432</v>
+        <v>691329</v>
       </c>
       <c r="R23" t="n">
-        <v>6657786</v>
+        <v>6657950</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3170,7 +3170,7 @@
         <v>126907497</v>
       </c>
       <c r="B24" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>126905851</v>
       </c>
       <c r="B25" t="n">
-        <v>91955</v>
+        <v>91959</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>126905916</v>
       </c>
       <c r="B26" t="n">
-        <v>85036</v>
+        <v>85040</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>126909251</v>
       </c>
       <c r="B27" t="n">
-        <v>85036</v>
+        <v>85040</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>126908119</v>
       </c>
       <c r="B28" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>126909234</v>
       </c>
       <c r="B29" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3773,45 +3773,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126908832</v>
+        <v>126909137</v>
       </c>
       <c r="B30" t="n">
-        <v>100625</v>
+        <v>98447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691331</v>
+        <v>691384</v>
       </c>
       <c r="R30" t="n">
-        <v>6657987</v>
+        <v>6657854</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3870,54 +3879,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126909137</v>
+        <v>126908832</v>
       </c>
       <c r="B31" t="n">
-        <v>98443</v>
+        <v>100629</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691384</v>
+        <v>691331</v>
       </c>
       <c r="R31" t="n">
-        <v>6657854</v>
+        <v>6657987</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3979,7 +3979,7 @@
         <v>126908066</v>
       </c>
       <c r="B32" t="n">
-        <v>8436</v>
+        <v>8439</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4073,10 +4073,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126907198</v>
+        <v>126908052</v>
       </c>
       <c r="B33" t="n">
-        <v>97321</v>
+        <v>100629</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4084,43 +4084,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>691387</v>
+        <v>691381</v>
       </c>
       <c r="R33" t="n">
-        <v>6657944</v>
+        <v>6658051</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4179,10 +4170,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126908052</v>
+        <v>126907198</v>
       </c>
       <c r="B34" t="n">
-        <v>100625</v>
+        <v>97325</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4190,34 +4181,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>691381</v>
+        <v>691387</v>
       </c>
       <c r="R34" t="n">
-        <v>6658051</v>
+        <v>6657944</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4279,7 +4279,7 @@
         <v>126906062</v>
       </c>
       <c r="B35" t="n">
-        <v>91340</v>
+        <v>91344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4373,37 +4373,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126908608</v>
+        <v>126906629</v>
       </c>
       <c r="B36" t="n">
-        <v>98443</v>
+        <v>105484</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4413,17 +4413,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691329</v>
+        <v>691376</v>
       </c>
       <c r="R36" t="n">
-        <v>6658013</v>
+        <v>6657865</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4479,37 +4479,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126906629</v>
+        <v>126908608</v>
       </c>
       <c r="B37" t="n">
-        <v>105478</v>
+        <v>98447</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4519,17 +4519,17 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691376</v>
+        <v>691329</v>
       </c>
       <c r="R37" t="n">
-        <v>6657865</v>
+        <v>6658013</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>126907654</v>
       </c>
       <c r="B38" t="n">
-        <v>5176</v>
+        <v>5177</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>126908912</v>
       </c>
       <c r="B39" t="n">
-        <v>5176</v>
+        <v>5177</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>126907715</v>
       </c>
       <c r="B40" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>126906867</v>
       </c>
       <c r="B41" t="n">
-        <v>8436</v>
+        <v>8439</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>126907755</v>
       </c>
       <c r="B42" t="n">
-        <v>105478</v>
+        <v>105484</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5093,48 +5093,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126907354</v>
+        <v>126908871</v>
       </c>
       <c r="B43" t="n">
-        <v>91955</v>
+        <v>57658</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>691389</v>
+        <v>691352</v>
       </c>
       <c r="R43" t="n">
-        <v>6657968</v>
+        <v>6657981</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5174,21 +5179,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5205,38 +5195,42 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126908871</v>
+        <v>126908462</v>
       </c>
       <c r="B44" t="n">
-        <v>57654</v>
+        <v>105484</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5245,13 +5239,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691352</v>
+        <v>691296</v>
       </c>
       <c r="R44" t="n">
-        <v>6657981</v>
+        <v>6658183</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5281,6 +5275,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Cirka</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5307,10 +5306,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126909078</v>
+        <v>126907354</v>
       </c>
       <c r="B45" t="n">
-        <v>8436</v>
+        <v>91959</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5318,37 +5317,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106554</v>
+        <v>1339</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691347</v>
+        <v>691389</v>
       </c>
       <c r="R45" t="n">
-        <v>6657905</v>
+        <v>6657968</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5388,6 +5387,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5404,10 +5418,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126907007</v>
+        <v>126909078</v>
       </c>
       <c r="B46" t="n">
-        <v>8436</v>
+        <v>8439</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5435,14 +5449,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691368</v>
+        <v>691347</v>
       </c>
       <c r="R46" t="n">
-        <v>6657895</v>
+        <v>6657905</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5501,10 +5515,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126908462</v>
+        <v>126907007</v>
       </c>
       <c r="B47" t="n">
-        <v>105478</v>
+        <v>8439</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5512,46 +5526,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>106554</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>691296</v>
+        <v>691368</v>
       </c>
       <c r="R47" t="n">
-        <v>6658183</v>
+        <v>6657895</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5581,11 +5586,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Cirka</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5615,7 +5615,7 @@
         <v>126909066</v>
       </c>
       <c r="B48" t="n">
-        <v>5176</v>
+        <v>5177</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5709,57 +5709,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126906755</v>
+        <v>126908159</v>
       </c>
       <c r="B49" t="n">
-        <v>98443</v>
+        <v>91295</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>691376</v>
+        <v>691373</v>
       </c>
       <c r="R49" t="n">
-        <v>6657865</v>
+        <v>6658096</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5818,7 +5809,7 @@
         <v>126906874</v>
       </c>
       <c r="B50" t="n">
-        <v>95796</v>
+        <v>95800</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5912,48 +5903,57 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126908159</v>
+        <v>126906755</v>
       </c>
       <c r="B51" t="n">
-        <v>91291</v>
+        <v>98447</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>691373</v>
+        <v>691376</v>
       </c>
       <c r="R51" t="n">
-        <v>6658096</v>
+        <v>6657865</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>126908952</v>
       </c>
       <c r="B52" t="n">
-        <v>8436</v>
+        <v>8439</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>126907554</v>
       </c>
       <c r="B53" t="n">
-        <v>5196</v>
+        <v>5197</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         <v>126908908</v>
       </c>
       <c r="B54" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6309,10 +6309,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126907301</v>
+        <v>126909033</v>
       </c>
       <c r="B55" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6349,17 +6349,17 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>691387</v>
+        <v>691336</v>
       </c>
       <c r="R55" t="n">
-        <v>6657944</v>
+        <v>6657914</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6415,10 +6415,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126909033</v>
+        <v>126907301</v>
       </c>
       <c r="B56" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6455,17 +6455,17 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>691336</v>
+        <v>691387</v>
       </c>
       <c r="R56" t="n">
-        <v>6657914</v>
+        <v>6657944</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6521,48 +6521,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126908472</v>
+        <v>126907540</v>
       </c>
       <c r="B57" t="n">
-        <v>91955</v>
+        <v>91688</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1339</v>
+        <v>2062</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>691283</v>
+        <v>691377</v>
       </c>
       <c r="R57" t="n">
-        <v>6658140</v>
+        <v>6658022</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6618,10 +6618,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126907540</v>
+        <v>126908731</v>
       </c>
       <c r="B58" t="n">
-        <v>91684</v>
+        <v>90867</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6629,34 +6629,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2062</v>
+        <v>5747</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>691377</v>
+        <v>691331</v>
       </c>
       <c r="R58" t="n">
-        <v>6658022</v>
+        <v>6657987</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6715,32 +6715,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126908731</v>
+        <v>126908472</v>
       </c>
       <c r="B59" t="n">
-        <v>90863</v>
+        <v>91959</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5747</v>
+        <v>1339</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6750,13 +6750,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>691331</v>
+        <v>691283</v>
       </c>
       <c r="R59" t="n">
-        <v>6657987</v>
+        <v>6658140</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>126907130</v>
       </c>
       <c r="B60" t="n">
-        <v>8436</v>
+        <v>8439</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6909,10 +6909,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126906449</v>
+        <v>126908164</v>
       </c>
       <c r="B61" t="n">
-        <v>91291</v>
+        <v>5177</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6920,37 +6920,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>691433</v>
+        <v>691373</v>
       </c>
       <c r="R61" t="n">
-        <v>6657859</v>
+        <v>6658096</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7006,10 +7006,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126908164</v>
+        <v>126906449</v>
       </c>
       <c r="B62" t="n">
-        <v>5176</v>
+        <v>91295</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7017,37 +7017,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>691373</v>
+        <v>691433</v>
       </c>
       <c r="R62" t="n">
-        <v>6658096</v>
+        <v>6657859</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>126951967</v>
       </c>
       <c r="B63" t="n">
-        <v>105297</v>
+        <v>105303</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 30443-2025 artfynd.xlsx
+++ b/artfynd/A 30443-2025 artfynd.xlsx
@@ -1958,45 +1958,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126909177</v>
+        <v>126907068</v>
       </c>
       <c r="B12" t="n">
-        <v>91330</v>
+        <v>98447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691383</v>
+        <v>691392</v>
       </c>
       <c r="R12" t="n">
-        <v>6657798</v>
+        <v>6657918</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2055,54 +2064,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126907068</v>
+        <v>126909177</v>
       </c>
       <c r="B13" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691392</v>
+        <v>691383</v>
       </c>
       <c r="R13" t="n">
-        <v>6657918</v>
+        <v>6657798</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2364,32 +2364,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126908154</v>
+        <v>126907984</v>
       </c>
       <c r="B16" t="n">
-        <v>91330</v>
+        <v>95800</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691373</v>
+        <v>691394</v>
       </c>
       <c r="R16" t="n">
-        <v>6658096</v>
+        <v>6658034</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2461,57 +2461,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126908037</v>
+        <v>126908154</v>
       </c>
       <c r="B17" t="n">
-        <v>95896</v>
+        <v>91330</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>210</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691381</v>
+        <v>691373</v>
       </c>
       <c r="R17" t="n">
-        <v>6658051</v>
+        <v>6658096</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2664,10 +2655,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126908926</v>
+        <v>126908037</v>
       </c>
       <c r="B19" t="n">
-        <v>8439</v>
+        <v>95896</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2675,34 +2666,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106554</v>
+        <v>210</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691339</v>
+        <v>691381</v>
       </c>
       <c r="R19" t="n">
-        <v>6657957</v>
+        <v>6658051</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126907984</v>
+        <v>126908926</v>
       </c>
       <c r="B20" t="n">
-        <v>95800</v>
+        <v>8439</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2772,21 +2772,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2818</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2796,13 +2796,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691394</v>
+        <v>691339</v>
       </c>
       <c r="R20" t="n">
-        <v>6658034</v>
+        <v>6657957</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3676,45 +3676,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126909234</v>
+        <v>126909137</v>
       </c>
       <c r="B29" t="n">
-        <v>80081</v>
+        <v>98447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691401</v>
+        <v>691384</v>
       </c>
       <c r="R29" t="n">
-        <v>6657770</v>
+        <v>6657854</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3773,54 +3782,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126909137</v>
+        <v>126908832</v>
       </c>
       <c r="B30" t="n">
-        <v>98447</v>
+        <v>100629</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691384</v>
+        <v>691331</v>
       </c>
       <c r="R30" t="n">
-        <v>6657854</v>
+        <v>6657987</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3879,10 +3879,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126908832</v>
+        <v>126909234</v>
       </c>
       <c r="B31" t="n">
-        <v>100629</v>
+        <v>80081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3890,34 +3890,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691331</v>
+        <v>691401</v>
       </c>
       <c r="R31" t="n">
-        <v>6657987</v>
+        <v>6657770</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4073,10 +4073,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126908052</v>
+        <v>126907198</v>
       </c>
       <c r="B33" t="n">
-        <v>100629</v>
+        <v>97325</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4084,34 +4084,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>691381</v>
+        <v>691387</v>
       </c>
       <c r="R33" t="n">
-        <v>6658051</v>
+        <v>6657944</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4170,10 +4179,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126907198</v>
+        <v>126908052</v>
       </c>
       <c r="B34" t="n">
-        <v>97325</v>
+        <v>100629</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4181,43 +4190,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>691387</v>
+        <v>691381</v>
       </c>
       <c r="R34" t="n">
-        <v>6657944</v>
+        <v>6658051</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4373,37 +4373,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126906629</v>
+        <v>126908608</v>
       </c>
       <c r="B36" t="n">
-        <v>105484</v>
+        <v>98447</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4413,17 +4413,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691376</v>
+        <v>691329</v>
       </c>
       <c r="R36" t="n">
-        <v>6657865</v>
+        <v>6658013</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4479,37 +4479,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126908608</v>
+        <v>126906629</v>
       </c>
       <c r="B37" t="n">
-        <v>98447</v>
+        <v>105484</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4519,17 +4519,17 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691329</v>
+        <v>691376</v>
       </c>
       <c r="R37" t="n">
-        <v>6658013</v>
+        <v>6657865</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5195,10 +5195,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126908462</v>
+        <v>126907354</v>
       </c>
       <c r="B44" t="n">
-        <v>105484</v>
+        <v>91959</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5206,43 +5206,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221144</v>
+        <v>1339</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691296</v>
+        <v>691389</v>
       </c>
       <c r="R44" t="n">
-        <v>6658183</v>
+        <v>6657968</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5277,11 +5268,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Cirka</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5290,6 +5276,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5306,10 +5307,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126907354</v>
+        <v>126909078</v>
       </c>
       <c r="B45" t="n">
-        <v>91959</v>
+        <v>8439</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5317,37 +5318,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1339</v>
+        <v>106554</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691389</v>
+        <v>691347</v>
       </c>
       <c r="R45" t="n">
-        <v>6657968</v>
+        <v>6657905</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5387,21 +5388,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5418,7 +5404,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126909078</v>
+        <v>126907007</v>
       </c>
       <c r="B46" t="n">
         <v>8439</v>
@@ -5449,14 +5435,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691347</v>
+        <v>691368</v>
       </c>
       <c r="R46" t="n">
-        <v>6657905</v>
+        <v>6657895</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5515,10 +5501,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126907007</v>
+        <v>126908462</v>
       </c>
       <c r="B47" t="n">
-        <v>8439</v>
+        <v>105484</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5526,37 +5512,46 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106554</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>691368</v>
+        <v>691296</v>
       </c>
       <c r="R47" t="n">
-        <v>6657895</v>
+        <v>6658183</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5586,6 +5581,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Cirka</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5612,10 +5612,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126909066</v>
+        <v>126906874</v>
       </c>
       <c r="B48" t="n">
-        <v>5177</v>
+        <v>95800</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5623,37 +5623,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>691337</v>
+        <v>691382</v>
       </c>
       <c r="R48" t="n">
-        <v>6657892</v>
+        <v>6657874</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5806,10 +5806,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126906874</v>
+        <v>126909066</v>
       </c>
       <c r="B50" t="n">
-        <v>95800</v>
+        <v>5177</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5817,37 +5817,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691382</v>
+        <v>691337</v>
       </c>
       <c r="R50" t="n">
-        <v>6657874</v>
+        <v>6657892</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6009,45 +6009,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126908952</v>
+        <v>126908908</v>
       </c>
       <c r="B52" t="n">
-        <v>8439</v>
+        <v>98447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>691329</v>
+        <v>691331</v>
       </c>
       <c r="R52" t="n">
-        <v>6657950</v>
+        <v>6657987</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6106,10 +6115,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126907554</v>
+        <v>126908952</v>
       </c>
       <c r="B53" t="n">
-        <v>5197</v>
+        <v>8439</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6117,34 +6126,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>691373</v>
+        <v>691329</v>
       </c>
       <c r="R53" t="n">
-        <v>6658009</v>
+        <v>6657950</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6203,54 +6212,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126908908</v>
+        <v>126907554</v>
       </c>
       <c r="B54" t="n">
-        <v>98447</v>
+        <v>5197</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>691331</v>
+        <v>691373</v>
       </c>
       <c r="R54" t="n">
-        <v>6657987</v>
+        <v>6658009</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6521,10 +6521,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126907540</v>
+        <v>126908731</v>
       </c>
       <c r="B57" t="n">
-        <v>91688</v>
+        <v>90867</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6532,34 +6532,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2062</v>
+        <v>5747</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>691377</v>
+        <v>691331</v>
       </c>
       <c r="R57" t="n">
-        <v>6658022</v>
+        <v>6657987</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6618,32 +6618,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126908731</v>
+        <v>126908472</v>
       </c>
       <c r="B58" t="n">
-        <v>90867</v>
+        <v>91959</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5747</v>
+        <v>1339</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6653,13 +6653,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>691331</v>
+        <v>691283</v>
       </c>
       <c r="R58" t="n">
-        <v>6657987</v>
+        <v>6658140</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6715,10 +6715,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126908472</v>
+        <v>126907130</v>
       </c>
       <c r="B59" t="n">
-        <v>91959</v>
+        <v>8439</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6726,37 +6726,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1339</v>
+        <v>106554</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>691283</v>
+        <v>691416</v>
       </c>
       <c r="R59" t="n">
-        <v>6658140</v>
+        <v>6657910</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6812,32 +6812,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126907130</v>
+        <v>126907540</v>
       </c>
       <c r="B60" t="n">
-        <v>8439</v>
+        <v>91688</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106554</v>
+        <v>2062</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6847,10 +6847,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>691416</v>
+        <v>691377</v>
       </c>
       <c r="R60" t="n">
-        <v>6657910</v>
+        <v>6658022</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>

--- a/artfynd/A 30443-2025 artfynd.xlsx
+++ b/artfynd/A 30443-2025 artfynd.xlsx
@@ -1958,54 +1958,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126907068</v>
+        <v>126909177</v>
       </c>
       <c r="B12" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691392</v>
+        <v>691383</v>
       </c>
       <c r="R12" t="n">
-        <v>6657918</v>
+        <v>6657798</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2064,45 +2055,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126909177</v>
+        <v>126907068</v>
       </c>
       <c r="B13" t="n">
-        <v>91330</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691383</v>
+        <v>691392</v>
       </c>
       <c r="R13" t="n">
-        <v>6657798</v>
+        <v>6657918</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2964,45 +2964,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126906093</v>
+        <v>126909047</v>
       </c>
       <c r="B22" t="n">
-        <v>5177</v>
+        <v>98447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691432</v>
+        <v>691329</v>
       </c>
       <c r="R22" t="n">
-        <v>6657786</v>
+        <v>6657950</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3061,54 +3070,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126909047</v>
+        <v>126906093</v>
       </c>
       <c r="B23" t="n">
-        <v>98447</v>
+        <v>5177</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691329</v>
+        <v>691432</v>
       </c>
       <c r="R23" t="n">
-        <v>6657950</v>
+        <v>6657786</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3676,54 +3676,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126909137</v>
+        <v>126908832</v>
       </c>
       <c r="B29" t="n">
-        <v>98447</v>
+        <v>100629</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691384</v>
+        <v>691331</v>
       </c>
       <c r="R29" t="n">
-        <v>6657854</v>
+        <v>6657987</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3782,10 +3773,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126908832</v>
+        <v>126909234</v>
       </c>
       <c r="B30" t="n">
-        <v>100629</v>
+        <v>80081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3793,34 +3784,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691331</v>
+        <v>691401</v>
       </c>
       <c r="R30" t="n">
-        <v>6657987</v>
+        <v>6657770</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3879,45 +3870,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126909234</v>
+        <v>126909137</v>
       </c>
       <c r="B31" t="n">
-        <v>80081</v>
+        <v>98447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691401</v>
+        <v>691384</v>
       </c>
       <c r="R31" t="n">
-        <v>6657770</v>
+        <v>6657854</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3976,10 +3976,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126908066</v>
+        <v>126908052</v>
       </c>
       <c r="B32" t="n">
-        <v>8439</v>
+        <v>100629</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3987,21 +3987,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4073,10 +4073,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126907198</v>
+        <v>126908066</v>
       </c>
       <c r="B33" t="n">
-        <v>97325</v>
+        <v>8439</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4084,43 +4084,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>106554</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>691387</v>
+        <v>691381</v>
       </c>
       <c r="R33" t="n">
-        <v>6657944</v>
+        <v>6658051</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4179,10 +4170,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126908052</v>
+        <v>126907198</v>
       </c>
       <c r="B34" t="n">
-        <v>100629</v>
+        <v>97325</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4190,34 +4181,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>691381</v>
+        <v>691387</v>
       </c>
       <c r="R34" t="n">
-        <v>6658051</v>
+        <v>6657944</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -5612,48 +5612,57 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126906874</v>
+        <v>126906755</v>
       </c>
       <c r="B48" t="n">
-        <v>95800</v>
+        <v>98447</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2818</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>691382</v>
+        <v>691376</v>
       </c>
       <c r="R48" t="n">
-        <v>6657874</v>
+        <v>6657865</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5709,10 +5718,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126908159</v>
+        <v>126906874</v>
       </c>
       <c r="B49" t="n">
-        <v>91295</v>
+        <v>95800</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5720,34 +5729,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>691373</v>
+        <v>691382</v>
       </c>
       <c r="R49" t="n">
-        <v>6658096</v>
+        <v>6657874</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5806,10 +5815,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126909066</v>
+        <v>126908159</v>
       </c>
       <c r="B50" t="n">
-        <v>5177</v>
+        <v>91295</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5817,21 +5826,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5841,13 +5850,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691337</v>
+        <v>691373</v>
       </c>
       <c r="R50" t="n">
-        <v>6657892</v>
+        <v>6658096</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5903,54 +5912,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126906755</v>
+        <v>126909066</v>
       </c>
       <c r="B51" t="n">
-        <v>98447</v>
+        <v>5177</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>691376</v>
+        <v>691337</v>
       </c>
       <c r="R51" t="n">
-        <v>6657865</v>
+        <v>6657892</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6009,54 +6009,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126908908</v>
+        <v>126908952</v>
       </c>
       <c r="B52" t="n">
-        <v>98447</v>
+        <v>8439</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>691331</v>
+        <v>691329</v>
       </c>
       <c r="R52" t="n">
-        <v>6657987</v>
+        <v>6657950</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6115,10 +6106,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126908952</v>
+        <v>126907554</v>
       </c>
       <c r="B53" t="n">
-        <v>8439</v>
+        <v>5197</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6126,34 +6117,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>691329</v>
+        <v>691373</v>
       </c>
       <c r="R53" t="n">
-        <v>6657950</v>
+        <v>6658009</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6212,45 +6203,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126907554</v>
+        <v>126908908</v>
       </c>
       <c r="B54" t="n">
-        <v>5197</v>
+        <v>98447</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>691373</v>
+        <v>691331</v>
       </c>
       <c r="R54" t="n">
-        <v>6658009</v>
+        <v>6657987</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6521,32 +6521,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126908731</v>
+        <v>126908472</v>
       </c>
       <c r="B57" t="n">
-        <v>90867</v>
+        <v>91959</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5747</v>
+        <v>1339</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6556,13 +6556,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>691331</v>
+        <v>691283</v>
       </c>
       <c r="R57" t="n">
-        <v>6657987</v>
+        <v>6658140</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6618,48 +6618,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126908472</v>
+        <v>126907540</v>
       </c>
       <c r="B58" t="n">
-        <v>91959</v>
+        <v>91688</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1339</v>
+        <v>2062</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>691283</v>
+        <v>691377</v>
       </c>
       <c r="R58" t="n">
-        <v>6658140</v>
+        <v>6658022</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6715,45 +6715,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126907130</v>
+        <v>126908731</v>
       </c>
       <c r="B59" t="n">
-        <v>8439</v>
+        <v>90867</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106554</v>
+        <v>5747</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>691416</v>
+        <v>691331</v>
       </c>
       <c r="R59" t="n">
-        <v>6657910</v>
+        <v>6657987</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6812,32 +6812,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126907540</v>
+        <v>126907130</v>
       </c>
       <c r="B60" t="n">
-        <v>91688</v>
+        <v>8439</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2062</v>
+        <v>106554</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6847,10 +6847,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>691377</v>
+        <v>691416</v>
       </c>
       <c r="R60" t="n">
-        <v>6658022</v>
+        <v>6657910</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6909,10 +6909,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126908164</v>
+        <v>126906449</v>
       </c>
       <c r="B61" t="n">
-        <v>5177</v>
+        <v>91295</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6920,37 +6920,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>691373</v>
+        <v>691433</v>
       </c>
       <c r="R61" t="n">
-        <v>6658096</v>
+        <v>6657859</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7006,10 +7006,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126906449</v>
+        <v>126908164</v>
       </c>
       <c r="B62" t="n">
-        <v>91295</v>
+        <v>5177</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7017,37 +7017,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>691433</v>
+        <v>691373</v>
       </c>
       <c r="R62" t="n">
-        <v>6657859</v>
+        <v>6658096</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>

--- a/artfynd/A 30443-2025 artfynd.xlsx
+++ b/artfynd/A 30443-2025 artfynd.xlsx
@@ -2364,10 +2364,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126907984</v>
+        <v>126908037</v>
       </c>
       <c r="B16" t="n">
-        <v>95800</v>
+        <v>95896</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,37 +2375,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691394</v>
+        <v>691381</v>
       </c>
       <c r="R16" t="n">
-        <v>6658034</v>
+        <v>6658051</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2461,32 +2470,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126908154</v>
+        <v>126907984</v>
       </c>
       <c r="B17" t="n">
-        <v>91330</v>
+        <v>95800</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2496,10 +2505,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691373</v>
+        <v>691394</v>
       </c>
       <c r="R17" t="n">
-        <v>6658096</v>
+        <v>6658034</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2558,7 +2567,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126906047</v>
+        <v>126908154</v>
       </c>
       <c r="B18" t="n">
         <v>91330</v>
@@ -2589,14 +2598,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691432</v>
+        <v>691373</v>
       </c>
       <c r="R18" t="n">
-        <v>6657786</v>
+        <v>6658096</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2655,57 +2664,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126908037</v>
+        <v>126906047</v>
       </c>
       <c r="B19" t="n">
-        <v>95896</v>
+        <v>91330</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>210</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691381</v>
+        <v>691432</v>
       </c>
       <c r="R19" t="n">
-        <v>6658051</v>
+        <v>6657786</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2964,54 +2964,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126909047</v>
+        <v>126906093</v>
       </c>
       <c r="B22" t="n">
-        <v>98447</v>
+        <v>5177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691329</v>
+        <v>691432</v>
       </c>
       <c r="R22" t="n">
-        <v>6657950</v>
+        <v>6657786</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3070,45 +3061,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126906093</v>
+        <v>126909047</v>
       </c>
       <c r="B23" t="n">
-        <v>5177</v>
+        <v>98447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691432</v>
+        <v>691329</v>
       </c>
       <c r="R23" t="n">
-        <v>6657786</v>
+        <v>6657950</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3676,45 +3676,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126908832</v>
+        <v>126909137</v>
       </c>
       <c r="B29" t="n">
-        <v>100629</v>
+        <v>98447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691331</v>
+        <v>691384</v>
       </c>
       <c r="R29" t="n">
-        <v>6657987</v>
+        <v>6657854</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3773,10 +3782,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126909234</v>
+        <v>126908832</v>
       </c>
       <c r="B30" t="n">
-        <v>80081</v>
+        <v>100629</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3784,34 +3793,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691401</v>
+        <v>691331</v>
       </c>
       <c r="R30" t="n">
-        <v>6657770</v>
+        <v>6657987</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3870,54 +3879,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126909137</v>
+        <v>126909234</v>
       </c>
       <c r="B31" t="n">
-        <v>98447</v>
+        <v>80081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691384</v>
+        <v>691401</v>
       </c>
       <c r="R31" t="n">
-        <v>6657854</v>
+        <v>6657770</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -5612,57 +5612,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126906755</v>
+        <v>126906874</v>
       </c>
       <c r="B48" t="n">
-        <v>98447</v>
+        <v>95800</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>2818</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>691376</v>
+        <v>691382</v>
       </c>
       <c r="R48" t="n">
-        <v>6657865</v>
+        <v>6657874</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5718,10 +5709,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126906874</v>
+        <v>126908159</v>
       </c>
       <c r="B49" t="n">
-        <v>95800</v>
+        <v>91295</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5729,34 +5720,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2818</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>691382</v>
+        <v>691373</v>
       </c>
       <c r="R49" t="n">
-        <v>6657874</v>
+        <v>6658096</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5815,10 +5806,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126908159</v>
+        <v>126909066</v>
       </c>
       <c r="B50" t="n">
-        <v>91295</v>
+        <v>5177</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5826,21 +5817,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5850,13 +5841,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691373</v>
+        <v>691337</v>
       </c>
       <c r="R50" t="n">
-        <v>6658096</v>
+        <v>6657892</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5912,45 +5903,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126909066</v>
+        <v>126906755</v>
       </c>
       <c r="B51" t="n">
-        <v>5177</v>
+        <v>98447</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>691337</v>
+        <v>691376</v>
       </c>
       <c r="R51" t="n">
-        <v>6657892</v>
+        <v>6657865</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6009,45 +6009,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126908952</v>
+        <v>126908908</v>
       </c>
       <c r="B52" t="n">
-        <v>8439</v>
+        <v>98447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>691329</v>
+        <v>691331</v>
       </c>
       <c r="R52" t="n">
-        <v>6657950</v>
+        <v>6657987</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6106,10 +6115,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126907554</v>
+        <v>126908952</v>
       </c>
       <c r="B53" t="n">
-        <v>5197</v>
+        <v>8439</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6117,34 +6126,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>691373</v>
+        <v>691329</v>
       </c>
       <c r="R53" t="n">
-        <v>6658009</v>
+        <v>6657950</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6203,54 +6212,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126908908</v>
+        <v>126907554</v>
       </c>
       <c r="B54" t="n">
-        <v>98447</v>
+        <v>5197</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>691331</v>
+        <v>691373</v>
       </c>
       <c r="R54" t="n">
-        <v>6657987</v>
+        <v>6658009</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6909,10 +6909,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126906449</v>
+        <v>126908164</v>
       </c>
       <c r="B61" t="n">
-        <v>91295</v>
+        <v>5177</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6920,37 +6920,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>691433</v>
+        <v>691373</v>
       </c>
       <c r="R61" t="n">
-        <v>6657859</v>
+        <v>6658096</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7006,10 +7006,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126908164</v>
+        <v>126906449</v>
       </c>
       <c r="B62" t="n">
-        <v>5177</v>
+        <v>91295</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7017,37 +7017,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>691373</v>
+        <v>691433</v>
       </c>
       <c r="R62" t="n">
-        <v>6658096</v>
+        <v>6657859</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>

--- a/artfynd/A 30443-2025 artfynd.xlsx
+++ b/artfynd/A 30443-2025 artfynd.xlsx
@@ -2058,7 +2058,7 @@
         <v>126907068</v>
       </c>
       <c r="B13" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>126907789</v>
       </c>
       <c r="B15" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2364,10 +2364,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126908037</v>
+        <v>126907984</v>
       </c>
       <c r="B16" t="n">
-        <v>95896</v>
+        <v>95800</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,46 +2375,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691381</v>
+        <v>691394</v>
       </c>
       <c r="R16" t="n">
-        <v>6658051</v>
+        <v>6658034</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2470,32 +2461,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126907984</v>
+        <v>126908154</v>
       </c>
       <c r="B17" t="n">
-        <v>95800</v>
+        <v>91330</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2505,10 +2496,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691394</v>
+        <v>691373</v>
       </c>
       <c r="R17" t="n">
-        <v>6658034</v>
+        <v>6658096</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2567,48 +2558,57 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126908154</v>
+        <v>126908037</v>
       </c>
       <c r="B18" t="n">
-        <v>91330</v>
+        <v>95896</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691373</v>
+        <v>691381</v>
       </c>
       <c r="R18" t="n">
-        <v>6658096</v>
+        <v>6658051</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>126907030</v>
       </c>
       <c r="B21" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>126909047</v>
       </c>
       <c r="B23" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>126908119</v>
       </c>
       <c r="B28" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>126909137</v>
       </c>
       <c r="B29" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>126908832</v>
       </c>
       <c r="B30" t="n">
-        <v>100629</v>
+        <v>100630</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3976,10 +3976,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126908052</v>
+        <v>126907198</v>
       </c>
       <c r="B32" t="n">
-        <v>100629</v>
+        <v>97325</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3987,34 +3987,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>691381</v>
+        <v>691387</v>
       </c>
       <c r="R32" t="n">
-        <v>6658051</v>
+        <v>6657944</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4073,10 +4082,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126908066</v>
+        <v>126908052</v>
       </c>
       <c r="B33" t="n">
-        <v>8439</v>
+        <v>100630</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4084,21 +4093,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4170,10 +4179,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126907198</v>
+        <v>126908066</v>
       </c>
       <c r="B34" t="n">
-        <v>97325</v>
+        <v>8439</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4181,43 +4190,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>106554</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>691387</v>
+        <v>691381</v>
       </c>
       <c r="R34" t="n">
-        <v>6657944</v>
+        <v>6658051</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4376,7 +4376,7 @@
         <v>126908608</v>
       </c>
       <c r="B36" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>126906629</v>
       </c>
       <c r="B37" t="n">
-        <v>105484</v>
+        <v>105486</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4585,45 +4585,54 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126907654</v>
+        <v>126907715</v>
       </c>
       <c r="B38" t="n">
-        <v>5177</v>
+        <v>98448</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691381</v>
+        <v>691363</v>
       </c>
       <c r="R38" t="n">
-        <v>6658039</v>
+        <v>6658060</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4682,7 +4691,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126908912</v>
+        <v>126907654</v>
       </c>
       <c r="B39" t="n">
         <v>5177</v>
@@ -4713,17 +4722,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691331</v>
+        <v>691381</v>
       </c>
       <c r="R39" t="n">
-        <v>6657987</v>
+        <v>6658039</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4779,57 +4788,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126907715</v>
+        <v>126908912</v>
       </c>
       <c r="B40" t="n">
-        <v>98447</v>
+        <v>5177</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>691363</v>
+        <v>691331</v>
       </c>
       <c r="R40" t="n">
-        <v>6658060</v>
+        <v>6657987</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>126907755</v>
       </c>
       <c r="B42" t="n">
-        <v>105484</v>
+        <v>105486</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5093,53 +5093,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126908871</v>
+        <v>126907354</v>
       </c>
       <c r="B43" t="n">
-        <v>57658</v>
+        <v>91959</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>691352</v>
+        <v>691389</v>
       </c>
       <c r="R43" t="n">
-        <v>6657981</v>
+        <v>6657968</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5179,6 +5174,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5195,48 +5205,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126907354</v>
+        <v>126908871</v>
       </c>
       <c r="B44" t="n">
-        <v>91959</v>
+        <v>57658</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691389</v>
+        <v>691352</v>
       </c>
       <c r="R44" t="n">
-        <v>6657968</v>
+        <v>6657981</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5276,21 +5291,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5307,10 +5307,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126909078</v>
+        <v>126908462</v>
       </c>
       <c r="B45" t="n">
-        <v>8439</v>
+        <v>105486</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5318,37 +5318,46 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106554</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691347</v>
+        <v>691296</v>
       </c>
       <c r="R45" t="n">
-        <v>6657905</v>
+        <v>6658183</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5378,6 +5387,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Cirka</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5404,7 +5418,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126907007</v>
+        <v>126909078</v>
       </c>
       <c r="B46" t="n">
         <v>8439</v>
@@ -5435,14 +5449,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691368</v>
+        <v>691347</v>
       </c>
       <c r="R46" t="n">
-        <v>6657895</v>
+        <v>6657905</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5501,10 +5515,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126908462</v>
+        <v>126907007</v>
       </c>
       <c r="B47" t="n">
-        <v>105484</v>
+        <v>8439</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5512,46 +5526,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>106554</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>691296</v>
+        <v>691368</v>
       </c>
       <c r="R47" t="n">
-        <v>6658183</v>
+        <v>6657895</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5581,11 +5586,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Cirka</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5612,10 +5612,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126906874</v>
+        <v>126908159</v>
       </c>
       <c r="B48" t="n">
-        <v>95800</v>
+        <v>91295</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5623,34 +5623,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2818</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>691382</v>
+        <v>691373</v>
       </c>
       <c r="R48" t="n">
-        <v>6657874</v>
+        <v>6658096</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5709,10 +5709,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126908159</v>
+        <v>126906874</v>
       </c>
       <c r="B49" t="n">
-        <v>91295</v>
+        <v>95800</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5720,34 +5720,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>691373</v>
+        <v>691382</v>
       </c>
       <c r="R49" t="n">
-        <v>6658096</v>
+        <v>6657874</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5906,7 +5906,7 @@
         <v>126906755</v>
       </c>
       <c r="B51" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6009,54 +6009,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126908908</v>
+        <v>126908952</v>
       </c>
       <c r="B52" t="n">
-        <v>98447</v>
+        <v>8439</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>691331</v>
+        <v>691329</v>
       </c>
       <c r="R52" t="n">
-        <v>6657987</v>
+        <v>6657950</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6115,10 +6106,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126908952</v>
+        <v>126907554</v>
       </c>
       <c r="B53" t="n">
-        <v>8439</v>
+        <v>5197</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6126,34 +6117,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>691329</v>
+        <v>691373</v>
       </c>
       <c r="R53" t="n">
-        <v>6657950</v>
+        <v>6658009</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6212,45 +6203,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126907554</v>
+        <v>126908908</v>
       </c>
       <c r="B54" t="n">
-        <v>5197</v>
+        <v>98448</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>691373</v>
+        <v>691331</v>
       </c>
       <c r="R54" t="n">
-        <v>6658009</v>
+        <v>6657987</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6312,7 +6312,7 @@
         <v>126909033</v>
       </c>
       <c r="B55" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>126907301</v>
       </c>
       <c r="B56" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6521,48 +6521,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126908472</v>
+        <v>126907540</v>
       </c>
       <c r="B57" t="n">
-        <v>91959</v>
+        <v>91688</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1339</v>
+        <v>2062</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>691283</v>
+        <v>691377</v>
       </c>
       <c r="R57" t="n">
-        <v>6658140</v>
+        <v>6658022</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6618,32 +6618,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126907540</v>
+        <v>126907130</v>
       </c>
       <c r="B58" t="n">
-        <v>91688</v>
+        <v>8439</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2062</v>
+        <v>106554</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>691377</v>
+        <v>691416</v>
       </c>
       <c r="R58" t="n">
-        <v>6658022</v>
+        <v>6657910</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6715,32 +6715,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126908731</v>
+        <v>126908472</v>
       </c>
       <c r="B59" t="n">
-        <v>90867</v>
+        <v>91959</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5747</v>
+        <v>1339</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6750,13 +6750,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>691331</v>
+        <v>691283</v>
       </c>
       <c r="R59" t="n">
-        <v>6657987</v>
+        <v>6658140</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6812,45 +6812,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126907130</v>
+        <v>126908731</v>
       </c>
       <c r="B60" t="n">
-        <v>8439</v>
+        <v>90867</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106554</v>
+        <v>5747</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>691416</v>
+        <v>691331</v>
       </c>
       <c r="R60" t="n">
-        <v>6657910</v>
+        <v>6657987</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6909,10 +6909,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126908164</v>
+        <v>126906449</v>
       </c>
       <c r="B61" t="n">
-        <v>5177</v>
+        <v>91295</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6920,37 +6920,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>691373</v>
+        <v>691433</v>
       </c>
       <c r="R61" t="n">
-        <v>6658096</v>
+        <v>6657859</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7006,10 +7006,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126906449</v>
+        <v>126908164</v>
       </c>
       <c r="B62" t="n">
-        <v>91295</v>
+        <v>5177</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7017,37 +7017,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>691433</v>
+        <v>691373</v>
       </c>
       <c r="R62" t="n">
-        <v>6657859</v>
+        <v>6658096</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>126951967</v>
       </c>
       <c r="B63" t="n">
-        <v>105303</v>
+        <v>105305</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 30443-2025 artfynd.xlsx
+++ b/artfynd/A 30443-2025 artfynd.xlsx
@@ -2761,45 +2761,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126908926</v>
+        <v>126907030</v>
       </c>
       <c r="B20" t="n">
-        <v>8439</v>
+        <v>98448</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691339</v>
+        <v>691371</v>
       </c>
       <c r="R20" t="n">
-        <v>6657957</v>
+        <v>6657926</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2858,54 +2867,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126907030</v>
+        <v>126908926</v>
       </c>
       <c r="B21" t="n">
-        <v>98448</v>
+        <v>8439</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691371</v>
+        <v>691339</v>
       </c>
       <c r="R21" t="n">
-        <v>6657926</v>
+        <v>6657957</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2964,45 +2964,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126906093</v>
+        <v>126909047</v>
       </c>
       <c r="B22" t="n">
-        <v>5177</v>
+        <v>98448</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691432</v>
+        <v>691329</v>
       </c>
       <c r="R22" t="n">
-        <v>6657786</v>
+        <v>6657950</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3061,54 +3070,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126909047</v>
+        <v>126906093</v>
       </c>
       <c r="B23" t="n">
-        <v>98448</v>
+        <v>5177</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691329</v>
+        <v>691432</v>
       </c>
       <c r="R23" t="n">
-        <v>6657950</v>
+        <v>6657786</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3676,54 +3676,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126909137</v>
+        <v>126909234</v>
       </c>
       <c r="B29" t="n">
-        <v>98448</v>
+        <v>80081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691384</v>
+        <v>691401</v>
       </c>
       <c r="R29" t="n">
-        <v>6657854</v>
+        <v>6657770</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3879,45 +3870,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126909234</v>
+        <v>126909137</v>
       </c>
       <c r="B31" t="n">
-        <v>80081</v>
+        <v>98448</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691401</v>
+        <v>691384</v>
       </c>
       <c r="R31" t="n">
-        <v>6657770</v>
+        <v>6657854</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3976,10 +3976,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126907198</v>
+        <v>126908066</v>
       </c>
       <c r="B32" t="n">
-        <v>97325</v>
+        <v>8439</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3987,43 +3987,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>106554</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>691387</v>
+        <v>691381</v>
       </c>
       <c r="R32" t="n">
-        <v>6657944</v>
+        <v>6658051</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4082,10 +4073,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126908052</v>
+        <v>126907198</v>
       </c>
       <c r="B33" t="n">
-        <v>100630</v>
+        <v>97325</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4093,34 +4084,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>691381</v>
+        <v>691387</v>
       </c>
       <c r="R33" t="n">
-        <v>6658051</v>
+        <v>6657944</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126908066</v>
+        <v>126908052</v>
       </c>
       <c r="B34" t="n">
-        <v>8439</v>
+        <v>100630</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4190,21 +4190,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -6309,7 +6309,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126909033</v>
+        <v>126907301</v>
       </c>
       <c r="B55" t="n">
         <v>98448</v>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6349,17 +6349,17 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>691336</v>
+        <v>691387</v>
       </c>
       <c r="R55" t="n">
-        <v>6657914</v>
+        <v>6657944</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126907301</v>
+        <v>126909033</v>
       </c>
       <c r="B56" t="n">
         <v>98448</v>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6455,17 +6455,17 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>691387</v>
+        <v>691336</v>
       </c>
       <c r="R56" t="n">
-        <v>6657944</v>
+        <v>6657914</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6618,45 +6618,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126907130</v>
+        <v>126908731</v>
       </c>
       <c r="B58" t="n">
-        <v>8439</v>
+        <v>90867</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106554</v>
+        <v>5747</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>691416</v>
+        <v>691331</v>
       </c>
       <c r="R58" t="n">
-        <v>6657910</v>
+        <v>6657987</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6812,45 +6812,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126908731</v>
+        <v>126907130</v>
       </c>
       <c r="B60" t="n">
-        <v>90867</v>
+        <v>8439</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5747</v>
+        <v>106554</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>691331</v>
+        <v>691416</v>
       </c>
       <c r="R60" t="n">
-        <v>6657987</v>
+        <v>6657910</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>

--- a/artfynd/A 30443-2025 artfynd.xlsx
+++ b/artfynd/A 30443-2025 artfynd.xlsx
@@ -1864,7 +1864,7 @@
         <v>126908435</v>
       </c>
       <c r="B11" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>126909177</v>
       </c>
       <c r="B12" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>126907068</v>
       </c>
       <c r="B13" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2161,45 +2161,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126906462</v>
+        <v>126907789</v>
       </c>
       <c r="B14" t="n">
-        <v>5177</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691433</v>
+        <v>691381</v>
       </c>
       <c r="R14" t="n">
-        <v>6657859</v>
+        <v>6658051</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2258,54 +2267,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126907789</v>
+        <v>126906462</v>
       </c>
       <c r="B15" t="n">
-        <v>98448</v>
+        <v>5177</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691381</v>
+        <v>691433</v>
       </c>
       <c r="R15" t="n">
-        <v>6658051</v>
+        <v>6657859</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2364,32 +2364,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126907984</v>
+        <v>126908154</v>
       </c>
       <c r="B16" t="n">
-        <v>95800</v>
+        <v>91332</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691394</v>
+        <v>691373</v>
       </c>
       <c r="R16" t="n">
-        <v>6658034</v>
+        <v>6658096</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2461,10 +2461,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126908154</v>
+        <v>126906047</v>
       </c>
       <c r="B17" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,14 +2492,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691373</v>
+        <v>691432</v>
       </c>
       <c r="R17" t="n">
-        <v>6658096</v>
+        <v>6657786</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2558,10 +2558,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126908037</v>
+        <v>126907984</v>
       </c>
       <c r="B18" t="n">
-        <v>95896</v>
+        <v>95802</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2569,46 +2569,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691381</v>
+        <v>691394</v>
       </c>
       <c r="R18" t="n">
-        <v>6658051</v>
+        <v>6658034</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2664,48 +2655,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126906047</v>
+        <v>126908037</v>
       </c>
       <c r="B19" t="n">
-        <v>91330</v>
+        <v>95898</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691432</v>
+        <v>691381</v>
       </c>
       <c r="R19" t="n">
-        <v>6657786</v>
+        <v>6658051</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>126907030</v>
       </c>
       <c r="B20" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2964,54 +2964,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126909047</v>
+        <v>126906093</v>
       </c>
       <c r="B22" t="n">
-        <v>98448</v>
+        <v>5177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691329</v>
+        <v>691432</v>
       </c>
       <c r="R22" t="n">
-        <v>6657950</v>
+        <v>6657786</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3070,45 +3061,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126906093</v>
+        <v>126909047</v>
       </c>
       <c r="B23" t="n">
-        <v>5177</v>
+        <v>98450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691432</v>
+        <v>691329</v>
       </c>
       <c r="R23" t="n">
-        <v>6657786</v>
+        <v>6657950</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3170,7 +3170,7 @@
         <v>126907497</v>
       </c>
       <c r="B24" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>126905851</v>
       </c>
       <c r="B25" t="n">
-        <v>91959</v>
+        <v>91961</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>126905916</v>
       </c>
       <c r="B26" t="n">
-        <v>85040</v>
+        <v>85042</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>126909251</v>
       </c>
       <c r="B27" t="n">
-        <v>85040</v>
+        <v>85042</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>126908119</v>
       </c>
       <c r="B28" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3676,45 +3676,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126909234</v>
+        <v>126909137</v>
       </c>
       <c r="B29" t="n">
-        <v>80081</v>
+        <v>98450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691401</v>
+        <v>691384</v>
       </c>
       <c r="R29" t="n">
-        <v>6657770</v>
+        <v>6657854</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3776,7 +3785,7 @@
         <v>126908832</v>
       </c>
       <c r="B30" t="n">
-        <v>100630</v>
+        <v>100632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3870,54 +3879,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126909137</v>
+        <v>126909234</v>
       </c>
       <c r="B31" t="n">
-        <v>98448</v>
+        <v>80083</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691384</v>
+        <v>691401</v>
       </c>
       <c r="R31" t="n">
-        <v>6657854</v>
+        <v>6657770</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4076,7 +4076,7 @@
         <v>126907198</v>
       </c>
       <c r="B33" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>126908052</v>
       </c>
       <c r="B34" t="n">
-        <v>100630</v>
+        <v>100632</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4276,45 +4276,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126906062</v>
+        <v>126908608</v>
       </c>
       <c r="B35" t="n">
-        <v>91344</v>
+        <v>98450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>691432</v>
+        <v>691329</v>
       </c>
       <c r="R35" t="n">
-        <v>6657786</v>
+        <v>6658013</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4373,37 +4382,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126908608</v>
+        <v>126906629</v>
       </c>
       <c r="B36" t="n">
-        <v>98448</v>
+        <v>105488</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4413,17 +4422,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691329</v>
+        <v>691376</v>
       </c>
       <c r="R36" t="n">
-        <v>6658013</v>
+        <v>6657865</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4479,57 +4488,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126906629</v>
+        <v>126906062</v>
       </c>
       <c r="B37" t="n">
-        <v>105486</v>
+        <v>91346</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221144</v>
+        <v>1204</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691376</v>
+        <v>691432</v>
       </c>
       <c r="R37" t="n">
-        <v>6657865</v>
+        <v>6657786</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4585,54 +4585,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126907715</v>
+        <v>126907654</v>
       </c>
       <c r="B38" t="n">
-        <v>98448</v>
+        <v>5177</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691363</v>
+        <v>691381</v>
       </c>
       <c r="R38" t="n">
-        <v>6658060</v>
+        <v>6658039</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4691,7 +4682,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126907654</v>
+        <v>126908912</v>
       </c>
       <c r="B39" t="n">
         <v>5177</v>
@@ -4722,17 +4713,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691381</v>
+        <v>691331</v>
       </c>
       <c r="R39" t="n">
-        <v>6658039</v>
+        <v>6657987</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4788,48 +4779,57 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126908912</v>
+        <v>126907715</v>
       </c>
       <c r="B40" t="n">
-        <v>5177</v>
+        <v>98450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>691331</v>
+        <v>691363</v>
       </c>
       <c r="R40" t="n">
-        <v>6657987</v>
+        <v>6658060</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>126907755</v>
       </c>
       <c r="B42" t="n">
-        <v>105486</v>
+        <v>105488</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5093,10 +5093,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126907354</v>
+        <v>126909078</v>
       </c>
       <c r="B43" t="n">
-        <v>91959</v>
+        <v>8439</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5104,37 +5104,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1339</v>
+        <v>106554</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>691389</v>
+        <v>691347</v>
       </c>
       <c r="R43" t="n">
-        <v>6657968</v>
+        <v>6657905</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5174,21 +5174,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5205,53 +5190,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126908871</v>
+        <v>126907354</v>
       </c>
       <c r="B44" t="n">
-        <v>57658</v>
+        <v>91961</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691352</v>
+        <v>691389</v>
       </c>
       <c r="R44" t="n">
-        <v>6657981</v>
+        <v>6657968</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5291,6 +5271,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5307,42 +5302,38 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126908462</v>
+        <v>126908871</v>
       </c>
       <c r="B45" t="n">
-        <v>105486</v>
+        <v>57660</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5351,13 +5342,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691296</v>
+        <v>691352</v>
       </c>
       <c r="R45" t="n">
-        <v>6658183</v>
+        <v>6657981</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5387,11 +5378,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Cirka</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5418,7 +5404,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126909078</v>
+        <v>126907007</v>
       </c>
       <c r="B46" t="n">
         <v>8439</v>
@@ -5449,14 +5435,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691347</v>
+        <v>691368</v>
       </c>
       <c r="R46" t="n">
-        <v>6657905</v>
+        <v>6657895</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5515,10 +5501,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126907007</v>
+        <v>126908462</v>
       </c>
       <c r="B47" t="n">
-        <v>8439</v>
+        <v>105488</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5526,37 +5512,46 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106554</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>691368</v>
+        <v>691296</v>
       </c>
       <c r="R47" t="n">
-        <v>6657895</v>
+        <v>6658183</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5586,6 +5581,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Cirka</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5612,10 +5612,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126908159</v>
+        <v>126906874</v>
       </c>
       <c r="B48" t="n">
-        <v>91295</v>
+        <v>95802</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5623,34 +5623,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>691373</v>
+        <v>691382</v>
       </c>
       <c r="R48" t="n">
-        <v>6658096</v>
+        <v>6657874</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5709,10 +5709,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126906874</v>
+        <v>126908159</v>
       </c>
       <c r="B49" t="n">
-        <v>95800</v>
+        <v>91297</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5720,34 +5720,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2818</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>691382</v>
+        <v>691373</v>
       </c>
       <c r="R49" t="n">
-        <v>6657874</v>
+        <v>6658096</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5906,7 +5906,7 @@
         <v>126906755</v>
       </c>
       <c r="B51" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         <v>126908908</v>
       </c>
       <c r="B54" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6309,10 +6309,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126907301</v>
+        <v>126909033</v>
       </c>
       <c r="B55" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6349,17 +6349,17 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>691387</v>
+        <v>691336</v>
       </c>
       <c r="R55" t="n">
-        <v>6657944</v>
+        <v>6657914</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6415,10 +6415,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126909033</v>
+        <v>126907301</v>
       </c>
       <c r="B56" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6455,17 +6455,17 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>691336</v>
+        <v>691387</v>
       </c>
       <c r="R56" t="n">
-        <v>6657914</v>
+        <v>6657944</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>126907540</v>
       </c>
       <c r="B57" t="n">
-        <v>91688</v>
+        <v>91690</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>126908731</v>
       </c>
       <c r="B58" t="n">
-        <v>90867</v>
+        <v>90869</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6715,10 +6715,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126908472</v>
+        <v>126907130</v>
       </c>
       <c r="B59" t="n">
-        <v>91959</v>
+        <v>8439</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6726,37 +6726,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1339</v>
+        <v>106554</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>691283</v>
+        <v>691416</v>
       </c>
       <c r="R59" t="n">
-        <v>6658140</v>
+        <v>6657910</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6812,10 +6812,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126907130</v>
+        <v>126908472</v>
       </c>
       <c r="B60" t="n">
-        <v>8439</v>
+        <v>91961</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6823,37 +6823,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106554</v>
+        <v>1339</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>691416</v>
+        <v>691283</v>
       </c>
       <c r="R60" t="n">
-        <v>6657910</v>
+        <v>6658140</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>126906449</v>
       </c>
       <c r="B61" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>126951967</v>
       </c>
       <c r="B63" t="n">
-        <v>105305</v>
+        <v>105307</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 30443-2025 artfynd.xlsx
+++ b/artfynd/A 30443-2025 artfynd.xlsx
@@ -2161,54 +2161,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126907789</v>
+        <v>126906462</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>5177</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691381</v>
+        <v>691433</v>
       </c>
       <c r="R14" t="n">
-        <v>6658051</v>
+        <v>6657859</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2267,45 +2258,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126906462</v>
+        <v>126907789</v>
       </c>
       <c r="B15" t="n">
-        <v>5177</v>
+        <v>98450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691433</v>
+        <v>691381</v>
       </c>
       <c r="R15" t="n">
-        <v>6657859</v>
+        <v>6658051</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2364,48 +2364,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126908154</v>
+        <v>126908037</v>
       </c>
       <c r="B16" t="n">
-        <v>91332</v>
+        <v>95898</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691373</v>
+        <v>691381</v>
       </c>
       <c r="R16" t="n">
-        <v>6658096</v>
+        <v>6658051</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2461,7 +2470,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126906047</v>
+        <v>126908154</v>
       </c>
       <c r="B17" t="n">
         <v>91332</v>
@@ -2492,14 +2501,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691432</v>
+        <v>691373</v>
       </c>
       <c r="R17" t="n">
-        <v>6657786</v>
+        <v>6658096</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2655,57 +2664,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126908037</v>
+        <v>126906047</v>
       </c>
       <c r="B19" t="n">
-        <v>95898</v>
+        <v>91332</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>210</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691381</v>
+        <v>691432</v>
       </c>
       <c r="R19" t="n">
-        <v>6658051</v>
+        <v>6657786</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2761,54 +2761,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126907030</v>
+        <v>126908926</v>
       </c>
       <c r="B20" t="n">
-        <v>98450</v>
+        <v>8439</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691371</v>
+        <v>691339</v>
       </c>
       <c r="R20" t="n">
-        <v>6657926</v>
+        <v>6657957</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2867,45 +2858,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126908926</v>
+        <v>126907030</v>
       </c>
       <c r="B21" t="n">
-        <v>8439</v>
+        <v>98450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691339</v>
+        <v>691371</v>
       </c>
       <c r="R21" t="n">
-        <v>6657957</v>
+        <v>6657926</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2964,45 +2964,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126906093</v>
+        <v>126909047</v>
       </c>
       <c r="B22" t="n">
-        <v>5177</v>
+        <v>98450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691432</v>
+        <v>691329</v>
       </c>
       <c r="R22" t="n">
-        <v>6657786</v>
+        <v>6657950</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3061,54 +3070,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126909047</v>
+        <v>126906093</v>
       </c>
       <c r="B23" t="n">
-        <v>98450</v>
+        <v>5177</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691329</v>
+        <v>691432</v>
       </c>
       <c r="R23" t="n">
-        <v>6657950</v>
+        <v>6657786</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3376,45 +3376,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126905916</v>
+        <v>126908119</v>
       </c>
       <c r="B26" t="n">
-        <v>85042</v>
+        <v>98450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1971</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stor sotdyna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Camarops polysperma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Mont.) J.H.Mill.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691453</v>
+        <v>691366</v>
       </c>
       <c r="R26" t="n">
-        <v>6657774</v>
+        <v>6658076</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3473,7 +3482,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126909251</v>
+        <v>126905916</v>
       </c>
       <c r="B27" t="n">
         <v>85042</v>
@@ -3508,10 +3517,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691377</v>
+        <v>691453</v>
       </c>
       <c r="R27" t="n">
-        <v>6657778</v>
+        <v>6657774</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3570,54 +3579,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126908119</v>
+        <v>126909251</v>
       </c>
       <c r="B28" t="n">
-        <v>98450</v>
+        <v>85042</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1971</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor sotdyna</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Camarops polysperma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Mont.) J.H.Mill.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>691366</v>
+        <v>691377</v>
       </c>
       <c r="R28" t="n">
-        <v>6658076</v>
+        <v>6657778</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4276,54 +4276,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126908608</v>
+        <v>126906062</v>
       </c>
       <c r="B35" t="n">
-        <v>98450</v>
+        <v>91346</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>691329</v>
+        <v>691432</v>
       </c>
       <c r="R35" t="n">
-        <v>6658013</v>
+        <v>6657786</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4488,45 +4479,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126906062</v>
+        <v>126908608</v>
       </c>
       <c r="B37" t="n">
-        <v>91346</v>
+        <v>98450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691432</v>
+        <v>691329</v>
       </c>
       <c r="R37" t="n">
-        <v>6657786</v>
+        <v>6658013</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4585,45 +4585,54 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126907654</v>
+        <v>126907715</v>
       </c>
       <c r="B38" t="n">
-        <v>5177</v>
+        <v>98450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691381</v>
+        <v>691363</v>
       </c>
       <c r="R38" t="n">
-        <v>6658039</v>
+        <v>6658060</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4682,7 +4691,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126908912</v>
+        <v>126907654</v>
       </c>
       <c r="B39" t="n">
         <v>5177</v>
@@ -4713,17 +4722,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691331</v>
+        <v>691381</v>
       </c>
       <c r="R39" t="n">
-        <v>6657987</v>
+        <v>6658039</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4779,57 +4788,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126907715</v>
+        <v>126908912</v>
       </c>
       <c r="B40" t="n">
-        <v>98450</v>
+        <v>5177</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>691363</v>
+        <v>691331</v>
       </c>
       <c r="R40" t="n">
-        <v>6658060</v>
+        <v>6657987</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5093,10 +5093,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126909078</v>
+        <v>126907354</v>
       </c>
       <c r="B43" t="n">
-        <v>8439</v>
+        <v>91961</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5104,37 +5104,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106554</v>
+        <v>1339</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>691347</v>
+        <v>691389</v>
       </c>
       <c r="R43" t="n">
-        <v>6657905</v>
+        <v>6657968</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5174,6 +5174,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5190,48 +5205,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126907354</v>
+        <v>126908871</v>
       </c>
       <c r="B44" t="n">
-        <v>91961</v>
+        <v>57660</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691389</v>
+        <v>691352</v>
       </c>
       <c r="R44" t="n">
-        <v>6657968</v>
+        <v>6657981</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5271,21 +5291,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5302,50 +5307,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126908871</v>
+        <v>126909078</v>
       </c>
       <c r="B45" t="n">
-        <v>57660</v>
+        <v>8439</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691352</v>
+        <v>691347</v>
       </c>
       <c r="R45" t="n">
-        <v>6657981</v>
+        <v>6657905</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5612,10 +5612,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126906874</v>
+        <v>126908159</v>
       </c>
       <c r="B48" t="n">
-        <v>95802</v>
+        <v>91297</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5623,34 +5623,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2818</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>691382</v>
+        <v>691373</v>
       </c>
       <c r="R48" t="n">
-        <v>6657874</v>
+        <v>6658096</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5709,10 +5709,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126908159</v>
+        <v>126909066</v>
       </c>
       <c r="B49" t="n">
-        <v>91297</v>
+        <v>5177</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5720,21 +5720,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5744,13 +5744,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>691373</v>
+        <v>691337</v>
       </c>
       <c r="R49" t="n">
-        <v>6658096</v>
+        <v>6657892</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5806,10 +5806,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126909066</v>
+        <v>126906874</v>
       </c>
       <c r="B50" t="n">
-        <v>5177</v>
+        <v>95802</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5817,37 +5817,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691337</v>
+        <v>691382</v>
       </c>
       <c r="R50" t="n">
-        <v>6657892</v>
+        <v>6657874</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6009,10 +6009,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126908952</v>
+        <v>126907554</v>
       </c>
       <c r="B52" t="n">
-        <v>8439</v>
+        <v>5197</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6020,34 +6020,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>691329</v>
+        <v>691373</v>
       </c>
       <c r="R52" t="n">
-        <v>6657950</v>
+        <v>6658009</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6106,10 +6106,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126907554</v>
+        <v>126908952</v>
       </c>
       <c r="B53" t="n">
-        <v>5197</v>
+        <v>8439</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6117,34 +6117,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>691373</v>
+        <v>691329</v>
       </c>
       <c r="R53" t="n">
-        <v>6658009</v>
+        <v>6657950</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6618,32 +6618,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126908731</v>
+        <v>126908472</v>
       </c>
       <c r="B58" t="n">
-        <v>90869</v>
+        <v>91961</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5747</v>
+        <v>1339</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6653,13 +6653,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>691331</v>
+        <v>691283</v>
       </c>
       <c r="R58" t="n">
-        <v>6657987</v>
+        <v>6658140</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6715,45 +6715,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126907130</v>
+        <v>126908731</v>
       </c>
       <c r="B59" t="n">
-        <v>8439</v>
+        <v>90869</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106554</v>
+        <v>5747</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>691416</v>
+        <v>691331</v>
       </c>
       <c r="R59" t="n">
-        <v>6657910</v>
+        <v>6657987</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6812,10 +6812,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126908472</v>
+        <v>126907130</v>
       </c>
       <c r="B60" t="n">
-        <v>91961</v>
+        <v>8439</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6823,37 +6823,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1339</v>
+        <v>106554</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>691283</v>
+        <v>691416</v>
       </c>
       <c r="R60" t="n">
-        <v>6658140</v>
+        <v>6657910</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>

--- a/artfynd/A 30443-2025 artfynd.xlsx
+++ b/artfynd/A 30443-2025 artfynd.xlsx
@@ -1864,7 +1864,7 @@
         <v>126908435</v>
       </c>
       <c r="B11" t="n">
-        <v>91332</v>
+        <v>91319</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1958,45 +1958,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126909177</v>
+        <v>126907068</v>
       </c>
       <c r="B12" t="n">
-        <v>91332</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691383</v>
+        <v>691392</v>
       </c>
       <c r="R12" t="n">
-        <v>6657798</v>
+        <v>6657918</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2055,54 +2064,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126907068</v>
+        <v>126909177</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>91319</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691392</v>
+        <v>691383</v>
       </c>
       <c r="R13" t="n">
-        <v>6657918</v>
+        <v>6657798</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2164,7 +2164,7 @@
         <v>126906462</v>
       </c>
       <c r="B14" t="n">
-        <v>5177</v>
+        <v>5176</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>126907789</v>
       </c>
       <c r="B15" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>126908037</v>
       </c>
       <c r="B16" t="n">
-        <v>95898</v>
+        <v>95885</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>126908154</v>
       </c>
       <c r="B17" t="n">
-        <v>91332</v>
+        <v>91319</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>126907984</v>
       </c>
       <c r="B18" t="n">
-        <v>95802</v>
+        <v>95789</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>126906047</v>
       </c>
       <c r="B19" t="n">
-        <v>91332</v>
+        <v>91319</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,45 +2761,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126908926</v>
+        <v>126907030</v>
       </c>
       <c r="B20" t="n">
-        <v>8439</v>
+        <v>98436</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691339</v>
+        <v>691371</v>
       </c>
       <c r="R20" t="n">
-        <v>6657957</v>
+        <v>6657926</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2858,54 +2867,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126907030</v>
+        <v>126908926</v>
       </c>
       <c r="B21" t="n">
-        <v>98450</v>
+        <v>8436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691371</v>
+        <v>691339</v>
       </c>
       <c r="R21" t="n">
-        <v>6657926</v>
+        <v>6657957</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2964,54 +2964,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126909047</v>
+        <v>126906093</v>
       </c>
       <c r="B22" t="n">
-        <v>98450</v>
+        <v>5176</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691329</v>
+        <v>691432</v>
       </c>
       <c r="R22" t="n">
-        <v>6657950</v>
+        <v>6657786</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3070,45 +3061,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126906093</v>
+        <v>126909047</v>
       </c>
       <c r="B23" t="n">
-        <v>5177</v>
+        <v>98436</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691432</v>
+        <v>691329</v>
       </c>
       <c r="R23" t="n">
-        <v>6657786</v>
+        <v>6657950</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3170,7 +3170,7 @@
         <v>126907497</v>
       </c>
       <c r="B24" t="n">
-        <v>91332</v>
+        <v>91319</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>126905851</v>
       </c>
       <c r="B25" t="n">
-        <v>91961</v>
+        <v>91948</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>126908119</v>
       </c>
       <c r="B26" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>126905916</v>
       </c>
       <c r="B27" t="n">
-        <v>85042</v>
+        <v>85033</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>126909251</v>
       </c>
       <c r="B28" t="n">
-        <v>85042</v>
+        <v>85033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>126909137</v>
       </c>
       <c r="B29" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3782,10 +3782,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126908832</v>
+        <v>126909234</v>
       </c>
       <c r="B30" t="n">
-        <v>100632</v>
+        <v>80074</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3793,34 +3793,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691331</v>
+        <v>691401</v>
       </c>
       <c r="R30" t="n">
-        <v>6657987</v>
+        <v>6657770</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3879,10 +3879,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126909234</v>
+        <v>126908832</v>
       </c>
       <c r="B31" t="n">
-        <v>80083</v>
+        <v>100618</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3890,34 +3890,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691401</v>
+        <v>691331</v>
       </c>
       <c r="R31" t="n">
-        <v>6657770</v>
+        <v>6657987</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3979,7 +3979,7 @@
         <v>126908066</v>
       </c>
       <c r="B32" t="n">
-        <v>8439</v>
+        <v>8436</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>126907198</v>
       </c>
       <c r="B33" t="n">
-        <v>97327</v>
+        <v>97314</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>126908052</v>
       </c>
       <c r="B34" t="n">
-        <v>100632</v>
+        <v>100618</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>126906062</v>
       </c>
       <c r="B35" t="n">
-        <v>91346</v>
+        <v>91333</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4373,37 +4373,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126906629</v>
+        <v>126908608</v>
       </c>
       <c r="B36" t="n">
-        <v>105488</v>
+        <v>98436</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4413,17 +4413,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691376</v>
+        <v>691329</v>
       </c>
       <c r="R36" t="n">
-        <v>6657865</v>
+        <v>6658013</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4479,37 +4479,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126908608</v>
+        <v>126906629</v>
       </c>
       <c r="B37" t="n">
-        <v>98450</v>
+        <v>105471</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4519,17 +4519,17 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691329</v>
+        <v>691376</v>
       </c>
       <c r="R37" t="n">
-        <v>6658013</v>
+        <v>6657865</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>126907715</v>
       </c>
       <c r="B38" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>126907654</v>
       </c>
       <c r="B39" t="n">
-        <v>5177</v>
+        <v>5176</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>126908912</v>
       </c>
       <c r="B40" t="n">
-        <v>5177</v>
+        <v>5176</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>126906867</v>
       </c>
       <c r="B41" t="n">
-        <v>8439</v>
+        <v>8436</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>126907755</v>
       </c>
       <c r="B42" t="n">
-        <v>105488</v>
+        <v>105471</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>126907354</v>
       </c>
       <c r="B43" t="n">
-        <v>91961</v>
+        <v>91948</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>126908871</v>
       </c>
       <c r="B44" t="n">
-        <v>57660</v>
+        <v>57654</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>126909078</v>
       </c>
       <c r="B45" t="n">
-        <v>8439</v>
+        <v>8436</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         <v>126907007</v>
       </c>
       <c r="B46" t="n">
-        <v>8439</v>
+        <v>8436</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>126908462</v>
       </c>
       <c r="B47" t="n">
-        <v>105488</v>
+        <v>105471</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5612,10 +5612,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126908159</v>
+        <v>126906874</v>
       </c>
       <c r="B48" t="n">
-        <v>91297</v>
+        <v>95789</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5623,34 +5623,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>691373</v>
+        <v>691382</v>
       </c>
       <c r="R48" t="n">
-        <v>6658096</v>
+        <v>6657874</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5709,10 +5709,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126909066</v>
+        <v>126908159</v>
       </c>
       <c r="B49" t="n">
-        <v>5177</v>
+        <v>91284</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5720,21 +5720,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5744,13 +5744,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>691337</v>
+        <v>691373</v>
       </c>
       <c r="R49" t="n">
-        <v>6657892</v>
+        <v>6658096</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5806,10 +5806,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126906874</v>
+        <v>126909066</v>
       </c>
       <c r="B50" t="n">
-        <v>95802</v>
+        <v>5176</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5817,37 +5817,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691382</v>
+        <v>691337</v>
       </c>
       <c r="R50" t="n">
-        <v>6657874</v>
+        <v>6657892</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>126906755</v>
       </c>
       <c r="B51" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6009,45 +6009,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126907554</v>
+        <v>126908908</v>
       </c>
       <c r="B52" t="n">
-        <v>5197</v>
+        <v>98436</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>691373</v>
+        <v>691331</v>
       </c>
       <c r="R52" t="n">
-        <v>6658009</v>
+        <v>6657987</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6106,10 +6115,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126908952</v>
+        <v>126907554</v>
       </c>
       <c r="B53" t="n">
-        <v>8439</v>
+        <v>5196</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6117,34 +6126,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>691329</v>
+        <v>691373</v>
       </c>
       <c r="R53" t="n">
-        <v>6657950</v>
+        <v>6658009</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6203,54 +6212,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126908908</v>
+        <v>126908952</v>
       </c>
       <c r="B54" t="n">
-        <v>98450</v>
+        <v>8436</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>691331</v>
+        <v>691329</v>
       </c>
       <c r="R54" t="n">
-        <v>6657987</v>
+        <v>6657950</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6312,7 +6312,7 @@
         <v>126909033</v>
       </c>
       <c r="B55" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>126907301</v>
       </c>
       <c r="B56" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6521,10 +6521,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126907540</v>
+        <v>126908731</v>
       </c>
       <c r="B57" t="n">
-        <v>91690</v>
+        <v>90856</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6532,34 +6532,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2062</v>
+        <v>5747</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>691377</v>
+        <v>691331</v>
       </c>
       <c r="R57" t="n">
-        <v>6658022</v>
+        <v>6657987</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6618,48 +6618,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126908472</v>
+        <v>126907540</v>
       </c>
       <c r="B58" t="n">
-        <v>91961</v>
+        <v>91677</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1339</v>
+        <v>2062</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>691283</v>
+        <v>691377</v>
       </c>
       <c r="R58" t="n">
-        <v>6658140</v>
+        <v>6658022</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6715,32 +6715,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126908731</v>
+        <v>126908472</v>
       </c>
       <c r="B59" t="n">
-        <v>90869</v>
+        <v>91948</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5747</v>
+        <v>1339</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6750,13 +6750,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>691331</v>
+        <v>691283</v>
       </c>
       <c r="R59" t="n">
-        <v>6657987</v>
+        <v>6658140</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>126907130</v>
       </c>
       <c r="B60" t="n">
-        <v>8439</v>
+        <v>8436</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>126906449</v>
       </c>
       <c r="B61" t="n">
-        <v>91297</v>
+        <v>91284</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>126908164</v>
       </c>
       <c r="B62" t="n">
-        <v>5177</v>
+        <v>5176</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>126951967</v>
       </c>
       <c r="B63" t="n">
-        <v>105307</v>
+        <v>105290</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 30443-2025 artfynd.xlsx
+++ b/artfynd/A 30443-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>56220938</v>
       </c>
       <c r="B2" t="n">
-        <v>90642</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691418.7379487255</v>
+        <v>691419</v>
       </c>
       <c r="R2" t="n">
-        <v>6657889.149663398</v>
+        <v>6657889</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2009-09-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-09-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -806,37 +791,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69530048</v>
+        <v>56220941</v>
       </c>
       <c r="B3" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4368</v>
+        <v>150</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -855,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691447.5148283313</v>
+        <v>691616</v>
       </c>
       <c r="R3" t="n">
-        <v>6657769.923494189</v>
+        <v>6657994</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,27 +865,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2002-08-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2002-08-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-09</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ca. 10 ex. under gran.</t>
+          <t>Ca. 10 ex. i äldre, grandominerad barrskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +889,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Äldre barrskog.</t>
+          <t>Äldre, grandominerad barrskog.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -937,62 +907,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>69530049</v>
+        <v>126908037</v>
       </c>
       <c r="B4" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Österbyggeby S om Aspdalssjön, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691430.6162908187</v>
+        <v>691381</v>
       </c>
       <c r="R4" t="n">
-        <v>6657747.505062678</v>
+        <v>6658051</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1016,27 +981,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2002-08-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2002-08-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ca. 20 ex. under gran.</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,68 +997,58 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Äldre barrskog.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>69530047</v>
+        <v>69530029</v>
       </c>
       <c r="B5" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>788</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1117,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691456.958835529</v>
+        <v>691605</v>
       </c>
       <c r="R5" t="n">
-        <v>6657790.952495833</v>
+        <v>6657984</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,27 +1087,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2002-08-22</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2002-08-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>5 ex. under gran.</t>
+          <t>3 dm2 i bökspår efter vildsvin, i äldre, grandominerad barrskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1181,7 +1111,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Äldre barrskog.</t>
+          <t>Äldre, grandominerad barrskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1199,15 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>69563196</v>
+        <v>126906047</v>
       </c>
       <c r="B6" t="n">
-        <v>88953</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,43 +1140,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5754</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Österbyggeby S om Aspdalssjön, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691460.1241270447</v>
+        <v>691432</v>
       </c>
       <c r="R6" t="n">
-        <v>6657797.629093065</v>
+        <v>6657786</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,27 +1194,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2009-09-09</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2009-09-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>1 ex. i äldre, grandominerad barrskog.</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1309,80 +1210,61 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Äldre, grandominerad barrskog.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>74822141</v>
+        <v>126907497</v>
       </c>
       <c r="B7" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Österbyggeby S om Aspdalssjön, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691319.5699299885</v>
+        <v>691377</v>
       </c>
       <c r="R7" t="n">
-        <v>6658078.846120183</v>
+        <v>6658022</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1409,27 +1291,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2002-08-15</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2002-08-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>4 cm2 på stammen av levande asp, omkr. 210 cm.</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1440,85 +1307,61 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stammen av levande asp. # Asp</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>75093049</v>
+        <v>126908154</v>
       </c>
       <c r="B8" t="n">
-        <v>90366</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5836</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pers.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Österbyggeby S om Aspdalssjön, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691382.8749446429</v>
+        <v>691373</v>
       </c>
       <c r="R8" t="n">
-        <v>6658144.745931159</v>
+        <v>6658096</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1545,27 +1388,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2002-08-15</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2002-08-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>1 ex.</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1576,79 +1404,64 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre barrskog.</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>75192157</v>
+        <v>126908429</v>
       </c>
       <c r="B9" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Österbyggeby S om Aspdalssjön, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691428.8742698682</v>
+        <v>691296</v>
       </c>
       <c r="R9" t="n">
-        <v>6657742.405189798</v>
+        <v>6658183</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1672,27 +1485,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2002-08-22</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2002-08-22</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gnagspår och kläckhål i barken på levande gran, omkr. 158 cm.</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1703,81 +1501,61 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>75192159</v>
+        <v>126909177</v>
       </c>
       <c r="B10" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Österbyggeby S om Aspdalssjön, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691279.3134968636</v>
+        <v>691383</v>
       </c>
       <c r="R10" t="n">
-        <v>6658090.779595352</v>
+        <v>6657798</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1804,27 +1582,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2002-08-22</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2002-08-22</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gnagspår och kläckhål i barken på levande gran, omkr. 149 cm.</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1835,74 +1598,64 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126908435</v>
+        <v>126906062</v>
       </c>
       <c r="B11" t="n">
-        <v>91332</v>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691296</v>
+        <v>691432</v>
       </c>
       <c r="R11" t="n">
-        <v>6658183</v>
+        <v>6657786</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1958,32 +1711,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126909177</v>
+        <v>126905851</v>
       </c>
       <c r="B12" t="n">
-        <v>91332</v>
+        <v>92564</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1993,10 +1746,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691383</v>
+        <v>691458</v>
       </c>
       <c r="R12" t="n">
-        <v>6657798</v>
+        <v>6657753</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2039,6 +1792,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2055,57 +1823,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126907068</v>
+        <v>126907354</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>92564</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691392</v>
+        <v>691389</v>
       </c>
       <c r="R13" t="n">
-        <v>6657918</v>
+        <v>6657968</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2145,6 +1904,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2161,10 +1935,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126906462</v>
+        <v>126908472</v>
       </c>
       <c r="B14" t="n">
-        <v>5177</v>
+        <v>92564</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,34 +1946,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>1339</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691433</v>
+        <v>691283</v>
       </c>
       <c r="R14" t="n">
-        <v>6657859</v>
+        <v>6658140</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2258,57 +2032,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126907789</v>
+        <v>60836741</v>
       </c>
       <c r="B15" t="n">
-        <v>98450</v>
+        <v>93216</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby S om Aspdalssjön, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691381</v>
+        <v>691561</v>
       </c>
       <c r="R15" t="n">
-        <v>6658051</v>
+        <v>6658001</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2332,12 +2106,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2002-08-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2002-08-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2 ex. i mossvegetation under äldre gran. Hatt upp till 10 cm bred. Sporer 5 x 4 μm, knöliga. Hyfer med söljor.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2348,73 +2127,69 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Äldre barrskog.</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126908037</v>
+        <v>126905916</v>
       </c>
       <c r="B16" t="n">
-        <v>95898</v>
+        <v>85532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>210</v>
+        <v>1971</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stor sotdyna</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Camarops polysperma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Mont.) J.H.Mill.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691381</v>
+        <v>691453</v>
       </c>
       <c r="R16" t="n">
-        <v>6658051</v>
+        <v>6657774</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2470,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126908154</v>
+        <v>126909251</v>
       </c>
       <c r="B17" t="n">
-        <v>91332</v>
+        <v>85532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2481,34 +2256,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1971</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor sotdyna</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Camarops polysperma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Mont.) J.H.Mill.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691373</v>
+        <v>691377</v>
       </c>
       <c r="R17" t="n">
-        <v>6658096</v>
+        <v>6657778</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2567,45 +2342,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126907984</v>
+        <v>126907540</v>
       </c>
       <c r="B18" t="n">
-        <v>95802</v>
+        <v>92281</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2818</v>
+        <v>2062</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691394</v>
+        <v>691377</v>
       </c>
       <c r="R18" t="n">
-        <v>6658034</v>
+        <v>6658022</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2664,32 +2439,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126906047</v>
+        <v>126906874</v>
       </c>
       <c r="B19" t="n">
-        <v>91332</v>
+        <v>96458</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2699,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691432</v>
+        <v>691382</v>
       </c>
       <c r="R19" t="n">
-        <v>6657786</v>
+        <v>6657874</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2761,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126908926</v>
+        <v>126907984</v>
       </c>
       <c r="B20" t="n">
-        <v>8439</v>
+        <v>96458</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2772,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>2818</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2796,13 +2571,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691339</v>
+        <v>691394</v>
       </c>
       <c r="R20" t="n">
-        <v>6657957</v>
+        <v>6658034</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2858,32 +2633,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126907030</v>
+        <v>69530047</v>
       </c>
       <c r="B21" t="n">
-        <v>98450</v>
+        <v>93189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2893,22 +2668,22 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Österbyggeby S om Aspdalssjön, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691371</v>
+        <v>691457</v>
       </c>
       <c r="R21" t="n">
-        <v>6657926</v>
+        <v>6657791</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2932,12 +2707,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2002-08-22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2002-08-22</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>5 ex. under gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2948,70 +2728,75 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Äldre barrskog.</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126909047</v>
+        <v>69530049</v>
       </c>
       <c r="B22" t="n">
-        <v>98450</v>
+        <v>93189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby S om Aspdalssjön, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691329</v>
+        <v>691431</v>
       </c>
       <c r="R22" t="n">
-        <v>6657950</v>
+        <v>6657748</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3038,12 +2823,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2002-08-22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2002-08-22</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ca. 20 ex. under gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3054,61 +2844,75 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Äldre barrskog.</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126906093</v>
+        <v>69530030</v>
       </c>
       <c r="B23" t="n">
-        <v>5177</v>
+        <v>93215</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>4368</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Österbyggeby S om Aspdalssjön, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691432</v>
+        <v>691603</v>
       </c>
       <c r="R23" t="n">
-        <v>6657786</v>
+        <v>6657983</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3135,12 +2939,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2009-09-09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2009-09-09</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ca. 20 ex. i äldre, grandominerad barrskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3151,26 +2960,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Äldre, grandominerad barrskog.</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126907497</v>
+        <v>69530048</v>
       </c>
       <c r="B24" t="n">
-        <v>91332</v>
+        <v>93215</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3178,34 +2992,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>4368</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Österbyggeby S om Aspdalssjön, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691377</v>
+        <v>691448</v>
       </c>
       <c r="R24" t="n">
-        <v>6658022</v>
+        <v>6657770</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3232,12 +3055,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2002-08-22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2002-08-22</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ca. 10 ex. under gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3248,26 +3076,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Äldre barrskog.</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126905851</v>
+        <v>126906449</v>
       </c>
       <c r="B25" t="n">
-        <v>91961</v>
+        <v>91872</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3275,21 +3108,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1339</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3299,13 +3132,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691458</v>
+        <v>691433</v>
       </c>
       <c r="R25" t="n">
-        <v>6657753</v>
+        <v>6657859</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3345,21 +3178,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3376,54 +3194,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126908119</v>
+        <v>126908159</v>
       </c>
       <c r="B26" t="n">
-        <v>98450</v>
+        <v>91872</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691366</v>
+        <v>691373</v>
       </c>
       <c r="R26" t="n">
-        <v>6658076</v>
+        <v>6658096</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3482,45 +3291,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126905916</v>
+        <v>126908731</v>
       </c>
       <c r="B27" t="n">
-        <v>85042</v>
+        <v>91435</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1971</v>
+        <v>5747</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stor sotdyna</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Camarops polysperma</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Mont.) J.H.Mill.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691453</v>
+        <v>691331</v>
       </c>
       <c r="R27" t="n">
-        <v>6657774</v>
+        <v>6657987</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3579,10 +3388,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126909251</v>
+        <v>69563196</v>
       </c>
       <c r="B28" t="n">
-        <v>85042</v>
+        <v>91443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3590,34 +3399,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1971</v>
+        <v>5754</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stor sotdyna</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Camarops polysperma</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Mont.) J.H.Mill.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Österbyggeby S om Aspdalssjön, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>691377</v>
+        <v>691460</v>
       </c>
       <c r="R28" t="n">
-        <v>6657778</v>
+        <v>6657798</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3644,12 +3462,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2009-09-09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2009-09-09</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>1 ex. i äldre, grandominerad barrskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3660,70 +3483,75 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Äldre, grandominerad barrskog.</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126909137</v>
+        <v>75093049</v>
       </c>
       <c r="B29" t="n">
-        <v>98450</v>
+        <v>92928</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5836</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Österbyggeby S om Aspdalssjön, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691384</v>
+        <v>691383</v>
       </c>
       <c r="R29" t="n">
-        <v>6657854</v>
+        <v>6658145</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3750,12 +3578,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2002-08-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2002-08-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>1 ex.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3766,26 +3599,31 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Äldre barrskog.</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126908832</v>
+        <v>126908871</v>
       </c>
       <c r="B30" t="n">
-        <v>100632</v>
+        <v>57950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3793,34 +3631,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691331</v>
+        <v>691352</v>
       </c>
       <c r="R30" t="n">
-        <v>6657987</v>
+        <v>6657981</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3879,10 +3722,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126909234</v>
+        <v>126906093</v>
       </c>
       <c r="B31" t="n">
-        <v>80083</v>
+        <v>5179</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3890,21 +3733,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3914,10 +3757,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691401</v>
+        <v>691432</v>
       </c>
       <c r="R31" t="n">
-        <v>6657770</v>
+        <v>6657786</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3976,10 +3819,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126908066</v>
+        <v>126906462</v>
       </c>
       <c r="B32" t="n">
-        <v>8439</v>
+        <v>5179</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3987,34 +3830,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>691381</v>
+        <v>691433</v>
       </c>
       <c r="R32" t="n">
-        <v>6658051</v>
+        <v>6657859</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4073,10 +3916,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126907198</v>
+        <v>126907654</v>
       </c>
       <c r="B33" t="n">
-        <v>97327</v>
+        <v>5179</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4084,43 +3927,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>691387</v>
+        <v>691381</v>
       </c>
       <c r="R33" t="n">
-        <v>6657944</v>
+        <v>6658039</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4179,10 +4013,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126908052</v>
+        <v>126908164</v>
       </c>
       <c r="B34" t="n">
-        <v>100632</v>
+        <v>5179</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4190,21 +4024,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4214,13 +4048,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>691381</v>
+        <v>691373</v>
       </c>
       <c r="R34" t="n">
-        <v>6658051</v>
+        <v>6658096</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4276,45 +4110,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126906062</v>
+        <v>126908912</v>
       </c>
       <c r="B35" t="n">
-        <v>91346</v>
+        <v>5179</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1204</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>691432</v>
+        <v>691331</v>
       </c>
       <c r="R35" t="n">
-        <v>6657786</v>
+        <v>6657987</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4373,10 +4207,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126906629</v>
+        <v>126909066</v>
       </c>
       <c r="B36" t="n">
-        <v>105488</v>
+        <v>5179</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4384,43 +4218,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221144</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691376</v>
+        <v>691337</v>
       </c>
       <c r="R36" t="n">
-        <v>6657865</v>
+        <v>6657892</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4479,54 +4304,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126908608</v>
+        <v>75192157</v>
       </c>
       <c r="B37" t="n">
-        <v>98450</v>
+        <v>4781</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby S om Aspdalssjön, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691329</v>
+        <v>691429</v>
       </c>
       <c r="R37" t="n">
-        <v>6658013</v>
+        <v>6657742</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4553,12 +4374,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2002-08-22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2002-08-22</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Gnagspår och kläckhål i barken på levande gran, omkr. 158 cm.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4569,73 +4395,79 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126907715</v>
+        <v>75192159</v>
       </c>
       <c r="B38" t="n">
-        <v>98450</v>
+        <v>4781</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby S om Aspdalssjön, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691363</v>
+        <v>691279</v>
       </c>
       <c r="R38" t="n">
-        <v>6658060</v>
+        <v>6658091</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4659,12 +4491,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2002-08-22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2002-08-22</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Gnagspår och kläckhål i barken på levande gran, omkr. 149 cm.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4675,26 +4512,36 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126907654</v>
+        <v>126907554</v>
       </c>
       <c r="B39" t="n">
-        <v>5177</v>
+        <v>5199</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4702,21 +4549,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4726,13 +4573,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691381</v>
+        <v>691373</v>
       </c>
       <c r="R39" t="n">
-        <v>6658039</v>
+        <v>6658009</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4788,10 +4635,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126908912</v>
+        <v>126906867</v>
       </c>
       <c r="B40" t="n">
-        <v>5177</v>
+        <v>8444</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4799,34 +4646,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>691331</v>
+        <v>691382</v>
       </c>
       <c r="R40" t="n">
-        <v>6657987</v>
+        <v>6657874</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4885,10 +4732,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126906867</v>
+        <v>126907007</v>
       </c>
       <c r="B41" t="n">
-        <v>8439</v>
+        <v>8444</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4920,10 +4767,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>691382</v>
+        <v>691368</v>
       </c>
       <c r="R41" t="n">
-        <v>6657874</v>
+        <v>6657895</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4982,10 +4829,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126907755</v>
+        <v>126907130</v>
       </c>
       <c r="B42" t="n">
-        <v>105488</v>
+        <v>8444</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4993,46 +4840,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221144</v>
+        <v>106554</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>691363</v>
+        <v>691416</v>
       </c>
       <c r="R42" t="n">
-        <v>6658060</v>
+        <v>6657910</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5062,11 +4900,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Cirka</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5093,10 +4926,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126907354</v>
+        <v>126908066</v>
       </c>
       <c r="B43" t="n">
-        <v>91961</v>
+        <v>8444</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5104,34 +4937,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1339</v>
+        <v>106554</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>691389</v>
+        <v>691381</v>
       </c>
       <c r="R43" t="n">
-        <v>6657968</v>
+        <v>6658051</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5174,21 +5007,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5205,53 +5023,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126908871</v>
+        <v>126908926</v>
       </c>
       <c r="B44" t="n">
-        <v>57660</v>
+        <v>8444</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691352</v>
+        <v>691339</v>
       </c>
       <c r="R44" t="n">
-        <v>6657981</v>
+        <v>6657957</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5307,10 +5120,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126909078</v>
+        <v>126908952</v>
       </c>
       <c r="B45" t="n">
-        <v>8439</v>
+        <v>8444</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5342,10 +5155,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691347</v>
+        <v>691329</v>
       </c>
       <c r="R45" t="n">
-        <v>6657905</v>
+        <v>6657950</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5404,10 +5217,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126907007</v>
+        <v>126909078</v>
       </c>
       <c r="B46" t="n">
-        <v>8439</v>
+        <v>8444</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5435,14 +5248,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691368</v>
+        <v>691347</v>
       </c>
       <c r="R46" t="n">
-        <v>6657895</v>
+        <v>6657905</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5501,57 +5314,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126908462</v>
+        <v>126908302</v>
       </c>
       <c r="B47" t="n">
-        <v>105488</v>
+        <v>111390</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>219711</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>691296</v>
+        <v>691394</v>
       </c>
       <c r="R47" t="n">
-        <v>6658183</v>
+        <v>6658173</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5581,11 +5385,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Cirka</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5612,48 +5411,57 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126908159</v>
+        <v>126906755</v>
       </c>
       <c r="B48" t="n">
-        <v>91297</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>691373</v>
+        <v>691376</v>
       </c>
       <c r="R48" t="n">
-        <v>6658096</v>
+        <v>6657865</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5709,45 +5517,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126909066</v>
+        <v>126907030</v>
       </c>
       <c r="B49" t="n">
-        <v>5177</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>691337</v>
+        <v>691371</v>
       </c>
       <c r="R49" t="n">
-        <v>6657892</v>
+        <v>6657926</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5806,45 +5623,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126906874</v>
+        <v>126907068</v>
       </c>
       <c r="B50" t="n">
-        <v>95802</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2818</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691382</v>
+        <v>691392</v>
       </c>
       <c r="R50" t="n">
-        <v>6657874</v>
+        <v>6657918</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5903,10 +5729,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126906755</v>
+        <v>126907301</v>
       </c>
       <c r="B51" t="n">
-        <v>98450</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5933,7 +5759,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5947,10 +5773,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>691376</v>
+        <v>691387</v>
       </c>
       <c r="R51" t="n">
-        <v>6657865</v>
+        <v>6657944</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6009,48 +5835,57 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126907554</v>
+        <v>126907715</v>
       </c>
       <c r="B52" t="n">
-        <v>5197</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>691373</v>
+        <v>691363</v>
       </c>
       <c r="R52" t="n">
-        <v>6658009</v>
+        <v>6658060</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6106,48 +5941,57 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126908952</v>
+        <v>126907789</v>
       </c>
       <c r="B53" t="n">
-        <v>8439</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>691329</v>
+        <v>691381</v>
       </c>
       <c r="R53" t="n">
-        <v>6657950</v>
+        <v>6658051</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6203,10 +6047,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126908908</v>
+        <v>126908119</v>
       </c>
       <c r="B54" t="n">
-        <v>98450</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6233,7 +6077,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6247,10 +6091,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>691331</v>
+        <v>691366</v>
       </c>
       <c r="R54" t="n">
-        <v>6657987</v>
+        <v>6658076</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6309,10 +6153,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126909033</v>
+        <v>126908608</v>
       </c>
       <c r="B55" t="n">
-        <v>98450</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6339,7 +6183,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6353,10 +6197,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>691336</v>
+        <v>691329</v>
       </c>
       <c r="R55" t="n">
-        <v>6657914</v>
+        <v>6658013</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6415,10 +6259,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126907301</v>
+        <v>126908908</v>
       </c>
       <c r="B56" t="n">
-        <v>98450</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6445,7 +6289,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6455,17 +6299,17 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>691387</v>
+        <v>691331</v>
       </c>
       <c r="R56" t="n">
-        <v>6657944</v>
+        <v>6657987</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6521,10 +6365,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126907540</v>
+        <v>126909033</v>
       </c>
       <c r="B57" t="n">
-        <v>91690</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6532,34 +6376,43 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>691377</v>
+        <v>691336</v>
       </c>
       <c r="R57" t="n">
-        <v>6658022</v>
+        <v>6657914</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6618,48 +6471,57 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126908472</v>
+        <v>126909047</v>
       </c>
       <c r="B58" t="n">
-        <v>91961</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>691283</v>
+        <v>691329</v>
       </c>
       <c r="R58" t="n">
-        <v>6658140</v>
+        <v>6657950</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6715,10 +6577,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126908731</v>
+        <v>126909137</v>
       </c>
       <c r="B59" t="n">
-        <v>90869</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6726,34 +6588,43 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5747</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Christan</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>691331</v>
+        <v>691384</v>
       </c>
       <c r="R59" t="n">
-        <v>6657987</v>
+        <v>6657854</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6812,10 +6683,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126907130</v>
+        <v>74741672</v>
       </c>
       <c r="B60" t="n">
-        <v>8439</v>
+        <v>106061</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6823,34 +6694,43 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106554</v>
+        <v>221101</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Österbyggeby S om Aspdalssjön, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>691416</v>
+        <v>691490</v>
       </c>
       <c r="R60" t="n">
-        <v>6657910</v>
+        <v>6657788</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6877,12 +6757,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2002-08-22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2002-08-22</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ca. 10 m2 i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6897,22 +6782,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126906449</v>
+        <v>126951967</v>
       </c>
       <c r="B61" t="n">
-        <v>91297</v>
+        <v>106061</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6920,37 +6805,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>221101</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Österbyggeby, Upl</t>
+          <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>691433</v>
+        <v>691309</v>
       </c>
       <c r="R61" t="n">
-        <v>6657859</v>
+        <v>6658159</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7006,10 +6891,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126908164</v>
+        <v>126906629</v>
       </c>
       <c r="B62" t="n">
-        <v>5177</v>
+        <v>106244</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7017,37 +6902,46 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100526</v>
+        <v>221144</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Aspdalsviken, Upl</t>
+          <t>Österbyggeby, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>691373</v>
+        <v>691376</v>
       </c>
       <c r="R62" t="n">
-        <v>6658096</v>
+        <v>6657865</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7103,10 +6997,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126951967</v>
+        <v>126907755</v>
       </c>
       <c r="B63" t="n">
-        <v>105307</v>
+        <v>106244</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7114,37 +7008,46 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221101</v>
+        <v>221144</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Aspdalsviken, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>691309</v>
+        <v>691363</v>
       </c>
       <c r="R63" t="n">
-        <v>6658159</v>
+        <v>6658060</v>
       </c>
       <c r="S63" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7174,6 +7077,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Cirka</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7197,6 +7105,635 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>126908462</v>
+      </c>
+      <c r="B64" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Aspdalsviken, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>691296</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6658183</v>
+      </c>
+      <c r="S64" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Cirka</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>126907198</v>
+      </c>
+      <c r="B65" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Österbyggeby, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>691387</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6657944</v>
+      </c>
+      <c r="S65" t="n">
+        <v>15</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>126908052</v>
+      </c>
+      <c r="B66" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Aspdalsviken, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>691381</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6658051</v>
+      </c>
+      <c r="S66" t="n">
+        <v>15</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>126908832</v>
+      </c>
+      <c r="B67" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Aspdalsviken, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>691331</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6657987</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>74822141</v>
+      </c>
+      <c r="B68" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Österbyggeby S om Aspdalssjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>691320</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6658079</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2002-08-15</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2002-08-15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>4 cm2 på stammen av levande asp, omkr. 210 cm.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL68" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Stammen av levande asp. # Asp</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>126909234</v>
+      </c>
+      <c r="B69" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Österbyggeby, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>691401</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6657770</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
